--- a/research/traditional_assets/database/data/israel/israel_advertising.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_advertising.xlsx
@@ -1415,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1552,22 +1552,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1244862536613767</v>
+        <v>0.1242345852779555</v>
       </c>
       <c r="C2">
-        <v>697.3143258767632</v>
+        <v>691.429419485563</v>
       </c>
       <c r="D2">
-        <v>530.8143258767632</v>
+        <v>531.923419485563</v>
       </c>
       <c r="E2">
-        <v>-36.2</v>
+        <v>-29.206</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.994000000000001</v>
       </c>
       <c r="G2">
         <v>166.5</v>
@@ -1588,28 +1588,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3517982</v>
       </c>
       <c r="N2">
-        <v>23.02500000000001</v>
+        <v>22.6732018</v>
       </c>
       <c r="O2">
-        <v>5.295750000000002</v>
+        <v>5.214836414000001</v>
       </c>
       <c r="P2">
-        <v>17.72925</v>
+        <v>17.458365386</v>
       </c>
       <c r="Q2">
-        <v>82.82925</v>
+        <v>82.55836538599999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1244862536613767</v>
+        <v>0.1250982578565207</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.226718829172283</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>65.44945369248622</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1634,22 +1634,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1242345852779555</v>
+        <v>0.1239829168945343</v>
       </c>
       <c r="C3">
-        <v>691.429419485563</v>
+        <v>685.5491575213315</v>
       </c>
       <c r="D3">
-        <v>531.923419485563</v>
+        <v>533.0371575213316</v>
       </c>
       <c r="E3">
-        <v>-29.206</v>
+        <v>-22.212</v>
       </c>
       <c r="F3">
-        <v>6.994000000000001</v>
+        <v>13.988</v>
       </c>
       <c r="G3">
         <v>166.5</v>
@@ -1670,28 +1670,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M3">
-        <v>0.3517982</v>
+        <v>0.7035964</v>
       </c>
       <c r="N3">
-        <v>22.6732018</v>
+        <v>22.32140360000001</v>
       </c>
       <c r="O3">
-        <v>5.214836414000001</v>
+        <v>5.133922828000002</v>
       </c>
       <c r="P3">
-        <v>17.458365386</v>
+        <v>17.187480772</v>
       </c>
       <c r="Q3">
-        <v>82.55836538599999</v>
+        <v>82.28748077199999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1250982578565207</v>
+        <v>0.1257227519331983</v>
       </c>
       <c r="T3">
-        <v>1.226718829172283</v>
+        <v>1.23637955392557</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>65.44945369248622</v>
+        <v>32.72472684624312</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1716,22 +1716,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1239829168945343</v>
+        <v>0.1237312485111132</v>
       </c>
       <c r="C4">
-        <v>685.5491575213315</v>
+        <v>679.6735692186991</v>
       </c>
       <c r="D4">
-        <v>533.0371575213316</v>
+        <v>534.155569218699</v>
       </c>
       <c r="E4">
-        <v>-22.212</v>
+        <v>-15.218</v>
       </c>
       <c r="F4">
-        <v>13.988</v>
+        <v>20.982</v>
       </c>
       <c r="G4">
         <v>166.5</v>
@@ -1752,28 +1752,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M4">
-        <v>0.7035964</v>
+        <v>1.0553946</v>
       </c>
       <c r="N4">
-        <v>22.32140360000001</v>
+        <v>21.96960540000001</v>
       </c>
       <c r="O4">
-        <v>5.133922828000002</v>
+        <v>5.053009242000002</v>
       </c>
       <c r="P4">
-        <v>17.187480772</v>
+        <v>16.916596158</v>
       </c>
       <c r="Q4">
-        <v>82.28748077199999</v>
+        <v>82.016596158</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1257227519331983</v>
+        <v>0.1263601221764053</v>
       </c>
       <c r="T4">
-        <v>1.23637955392557</v>
+        <v>1.246239468879955</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.72472684624312</v>
+        <v>21.81648456416207</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1798,22 +1798,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1237312485111132</v>
+        <v>0.123479580127692</v>
       </c>
       <c r="C5">
-        <v>679.6735692186991</v>
+        <v>673.8026840581712</v>
       </c>
       <c r="D5">
-        <v>534.155569218699</v>
+        <v>535.2786840581712</v>
       </c>
       <c r="E5">
-        <v>-15.218</v>
+        <v>-8.224</v>
       </c>
       <c r="F5">
-        <v>20.982</v>
+        <v>27.976</v>
       </c>
       <c r="G5">
         <v>166.5</v>
@@ -1834,28 +1834,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M5">
-        <v>1.0553946</v>
+        <v>1.4071928</v>
       </c>
       <c r="N5">
-        <v>21.96960540000001</v>
+        <v>21.6178072</v>
       </c>
       <c r="O5">
-        <v>5.053009242000002</v>
+        <v>4.972095656000001</v>
       </c>
       <c r="P5">
-        <v>16.916596158</v>
+        <v>16.645711544</v>
       </c>
       <c r="Q5">
-        <v>82.016596158</v>
+        <v>81.745711544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1263601221764053</v>
+        <v>0.1270107709663458</v>
       </c>
       <c r="T5">
-        <v>1.246239468879955</v>
+        <v>1.256304798729222</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.81648456416207</v>
+        <v>16.36236342312155</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1880,22 +1880,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.123479580127692</v>
+        <v>0.1232279117442708</v>
       </c>
       <c r="C6">
-        <v>673.8026840581712</v>
+        <v>667.9365317687181</v>
       </c>
       <c r="D6">
-        <v>535.2786840581712</v>
+        <v>536.4065317687181</v>
       </c>
       <c r="E6">
-        <v>-8.224</v>
+        <v>-1.229999999999997</v>
       </c>
       <c r="F6">
-        <v>27.976</v>
+        <v>34.97000000000001</v>
       </c>
       <c r="G6">
         <v>166.5</v>
@@ -1916,28 +1916,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M6">
-        <v>1.4071928</v>
+        <v>1.758991</v>
       </c>
       <c r="N6">
-        <v>21.6178072</v>
+        <v>21.266009</v>
       </c>
       <c r="O6">
-        <v>4.972095656000001</v>
+        <v>4.891182070000001</v>
       </c>
       <c r="P6">
-        <v>16.645711544</v>
+        <v>16.37482693</v>
       </c>
       <c r="Q6">
-        <v>81.745711544</v>
+        <v>81.47482693000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1270107709663458</v>
+        <v>0.1276751176255482</v>
       </c>
       <c r="T6">
-        <v>1.256304798729222</v>
+        <v>1.266582030259527</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.36236342312155</v>
+        <v>13.08989073849724</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1962,22 +1962,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1232279117442708</v>
+        <v>0.1230455433608497</v>
       </c>
       <c r="C7">
-        <v>667.9365317687181</v>
+        <v>661.7627870990304</v>
       </c>
       <c r="D7">
-        <v>536.4065317687181</v>
+        <v>537.2267870990305</v>
       </c>
       <c r="E7">
-        <v>-1.229999999999997</v>
+        <v>5.764000000000003</v>
       </c>
       <c r="F7">
-        <v>34.97000000000001</v>
+        <v>41.96400000000001</v>
       </c>
       <c r="G7">
         <v>166.5</v>
@@ -1998,45 +1998,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M7">
-        <v>1.758991</v>
+        <v>2.1737352</v>
       </c>
       <c r="N7">
-        <v>21.266009</v>
+        <v>20.85126480000001</v>
       </c>
       <c r="O7">
-        <v>4.891182070000001</v>
+        <v>4.795790904000001</v>
       </c>
       <c r="P7">
-        <v>16.37482693</v>
+        <v>16.05547389600001</v>
       </c>
       <c r="Q7">
-        <v>81.47482693000001</v>
+        <v>81.155473896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1276751176255482</v>
+        <v>0.1283535993200528</v>
       </c>
       <c r="T7">
-        <v>1.266582030259527</v>
+        <v>1.277077926290477</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.23</v>
       </c>
       <c r="W7">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.08989073849724</v>
+        <v>10.59236654032193</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2044,22 +2044,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1230455433608497</v>
+        <v>0.1228970549774285</v>
       </c>
       <c r="C8">
-        <v>661.7627870990304</v>
+        <v>655.4385123333178</v>
       </c>
       <c r="D8">
-        <v>537.2267870990305</v>
+        <v>537.8965123333178</v>
       </c>
       <c r="E8">
-        <v>5.764000000000003</v>
+        <v>12.758</v>
       </c>
       <c r="F8">
-        <v>41.96400000000001</v>
+        <v>48.958</v>
       </c>
       <c r="G8">
         <v>166.5</v>
@@ -2080,45 +2080,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M8">
-        <v>2.1737352</v>
+        <v>2.619253</v>
       </c>
       <c r="N8">
-        <v>20.85126480000001</v>
+        <v>20.40574700000001</v>
       </c>
       <c r="O8">
-        <v>4.795790904000001</v>
+        <v>4.693321810000001</v>
       </c>
       <c r="P8">
-        <v>16.05547389600001</v>
+        <v>15.71242519</v>
       </c>
       <c r="Q8">
-        <v>81.155473896</v>
+        <v>80.81242519</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1283535993200528</v>
+        <v>0.1290466720187403</v>
       </c>
       <c r="T8">
-        <v>1.277077926290477</v>
+        <v>1.287799540515641</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.23</v>
       </c>
       <c r="W8">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.59236654032193</v>
+        <v>8.790674287669043</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2126,22 +2126,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1228970549774285</v>
+        <v>0.1226700265940073</v>
       </c>
       <c r="C9">
-        <v>655.4385123333179</v>
+        <v>649.4717098762892</v>
       </c>
       <c r="D9">
-        <v>537.8965123333179</v>
+        <v>538.9237098762892</v>
       </c>
       <c r="E9">
-        <v>12.75800000000001</v>
+        <v>19.752</v>
       </c>
       <c r="F9">
-        <v>48.95800000000001</v>
+        <v>55.95200000000001</v>
       </c>
       <c r="G9">
         <v>166.5</v>
@@ -2162,28 +2162,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M9">
-        <v>2.619253</v>
+        <v>2.993432</v>
       </c>
       <c r="N9">
-        <v>20.40574700000001</v>
+        <v>20.03156800000001</v>
       </c>
       <c r="O9">
-        <v>4.693321810000001</v>
+        <v>4.607260640000002</v>
       </c>
       <c r="P9">
-        <v>15.71242519</v>
+        <v>15.42430736000001</v>
       </c>
       <c r="Q9">
-        <v>80.81242519</v>
+        <v>80.52430735999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1290466720187403</v>
+        <v>0.1297548115152254</v>
       </c>
       <c r="T9">
-        <v>1.287799540515641</v>
+        <v>1.298754233310917</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.790674287669042</v>
+        <v>7.691840001710413</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2208,22 +2208,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1226700265940073</v>
+        <v>0.1224984382105862</v>
       </c>
       <c r="C10">
-        <v>649.4717098762892</v>
+        <v>643.2566741494468</v>
       </c>
       <c r="D10">
-        <v>538.9237098762892</v>
+        <v>539.7026741494468</v>
       </c>
       <c r="E10">
-        <v>19.752</v>
+        <v>26.746</v>
       </c>
       <c r="F10">
-        <v>55.95200000000001</v>
+        <v>62.94600000000001</v>
       </c>
       <c r="G10">
         <v>166.5</v>
@@ -2244,45 +2244,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M10">
-        <v>2.993432</v>
+        <v>3.4179678</v>
       </c>
       <c r="N10">
-        <v>20.03156800000001</v>
+        <v>19.60703220000001</v>
       </c>
       <c r="O10">
-        <v>4.607260640000002</v>
+        <v>4.509617406000002</v>
       </c>
       <c r="P10">
-        <v>15.42430736000001</v>
+        <v>15.097414794</v>
       </c>
       <c r="Q10">
-        <v>80.52430735999999</v>
+        <v>80.197414794</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1297548115152254</v>
+        <v>0.1304785145171277</v>
       </c>
       <c r="T10">
-        <v>1.298754233310917</v>
+        <v>1.309949688585211</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.23</v>
       </c>
       <c r="W10">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.691840001710413</v>
+        <v>6.736459015207809</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2290,22 +2290,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1224984382105862</v>
+        <v>0.122354569827165</v>
       </c>
       <c r="C11">
-        <v>643.2566741494468</v>
+        <v>636.9175348697063</v>
       </c>
       <c r="D11">
-        <v>539.7026741494468</v>
+        <v>540.3575348697063</v>
       </c>
       <c r="E11">
-        <v>26.746</v>
+        <v>33.73999999999999</v>
       </c>
       <c r="F11">
-        <v>62.94600000000001</v>
+        <v>69.94</v>
       </c>
       <c r="G11">
         <v>166.5</v>
@@ -2326,45 +2326,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M11">
-        <v>3.4179678</v>
+        <v>3.867682</v>
       </c>
       <c r="N11">
-        <v>19.60703220000001</v>
+        <v>19.15731800000001</v>
       </c>
       <c r="O11">
-        <v>4.509617406000002</v>
+        <v>4.406183140000002</v>
       </c>
       <c r="P11">
-        <v>15.097414794</v>
+        <v>14.75113486</v>
       </c>
       <c r="Q11">
-        <v>80.197414794</v>
+        <v>79.85113486</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1304785145171277</v>
+        <v>0.1312182998079611</v>
       </c>
       <c r="T11">
-        <v>1.309949688585211</v>
+        <v>1.321393931754488</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.23</v>
       </c>
       <c r="W11">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.736459015207809</v>
+        <v>5.953178156839163</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2372,22 +2372,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.122354569827165</v>
+        <v>0.1221414014437438</v>
       </c>
       <c r="C12">
-        <v>636.9175348697063</v>
+        <v>630.8967626728489</v>
       </c>
       <c r="D12">
-        <v>540.3575348697063</v>
+        <v>541.3307626728489</v>
       </c>
       <c r="E12">
-        <v>33.74000000000001</v>
+        <v>40.73400000000001</v>
       </c>
       <c r="F12">
-        <v>69.94000000000001</v>
+        <v>76.93400000000001</v>
       </c>
       <c r="G12">
         <v>166.5</v>
@@ -2408,28 +2408,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M12">
-        <v>3.867682000000001</v>
+        <v>4.254450200000001</v>
       </c>
       <c r="N12">
-        <v>19.157318</v>
+        <v>18.7705498</v>
       </c>
       <c r="O12">
-        <v>4.406183140000001</v>
+        <v>4.317226454000001</v>
       </c>
       <c r="P12">
-        <v>14.75113486</v>
+        <v>14.453323346</v>
       </c>
       <c r="Q12">
-        <v>79.85113486</v>
+        <v>79.553323346</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1312182998079611</v>
+        <v>0.1319747094873526</v>
       </c>
       <c r="T12">
-        <v>1.321393931754488</v>
+        <v>1.33309534892757</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.953178156839161</v>
+        <v>5.411980142581056</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2454,22 +2454,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1221414014437438</v>
+        <v>0.1219282330603227</v>
       </c>
       <c r="C13">
-        <v>630.8967626728489</v>
+        <v>624.879502526099</v>
       </c>
       <c r="D13">
-        <v>541.3307626728489</v>
+        <v>542.307502526099</v>
       </c>
       <c r="E13">
-        <v>40.73400000000001</v>
+        <v>47.72800000000001</v>
       </c>
       <c r="F13">
-        <v>76.93400000000001</v>
+        <v>83.92800000000001</v>
       </c>
       <c r="G13">
         <v>166.5</v>
@@ -2490,28 +2490,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M13">
-        <v>4.254450200000001</v>
+        <v>4.641218400000001</v>
       </c>
       <c r="N13">
-        <v>18.7705498</v>
+        <v>18.38378160000001</v>
       </c>
       <c r="O13">
-        <v>4.317226454000001</v>
+        <v>4.228269768000001</v>
       </c>
       <c r="P13">
-        <v>14.453323346</v>
+        <v>14.15551183200001</v>
       </c>
       <c r="Q13">
-        <v>79.553323346</v>
+        <v>79.255511832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1319747094873526</v>
+        <v>0.1327483102958212</v>
       </c>
       <c r="T13">
-        <v>1.33309534892757</v>
+        <v>1.345062707400039</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.411980142581056</v>
+        <v>4.960981797365968</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2536,22 +2536,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1219282330603227</v>
+        <v>0.1217150646769015</v>
       </c>
       <c r="C14">
-        <v>624.879502526099</v>
+        <v>618.8657734745223</v>
       </c>
       <c r="D14">
-        <v>542.307502526099</v>
+        <v>543.2877734745223</v>
       </c>
       <c r="E14">
-        <v>47.72800000000001</v>
+        <v>54.72200000000001</v>
       </c>
       <c r="F14">
-        <v>83.92800000000001</v>
+        <v>90.92200000000001</v>
       </c>
       <c r="G14">
         <v>166.5</v>
@@ -2572,28 +2572,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M14">
-        <v>4.641218400000001</v>
+        <v>5.027986600000001</v>
       </c>
       <c r="N14">
-        <v>18.38378160000001</v>
+        <v>17.9970134</v>
       </c>
       <c r="O14">
-        <v>4.228269768000001</v>
+        <v>4.139313082000001</v>
       </c>
       <c r="P14">
-        <v>14.15551183200001</v>
+        <v>13.857700318</v>
       </c>
       <c r="Q14">
-        <v>79.255511832</v>
+        <v>78.95770031799999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1327483102958212</v>
+        <v>0.1335396950309213</v>
       </c>
       <c r="T14">
-        <v>1.345062707400039</v>
+        <v>1.357305177561531</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.960981797365968</v>
+        <v>4.579367812953201</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2618,22 +2618,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1217150646769015</v>
+        <v>0.1217713962934803</v>
       </c>
       <c r="C15">
-        <v>618.8657734745223</v>
+        <v>611.6123839262866</v>
       </c>
       <c r="D15">
-        <v>543.2877734745223</v>
+        <v>543.0283839262867</v>
       </c>
       <c r="E15">
-        <v>54.72200000000001</v>
+        <v>61.71600000000002</v>
       </c>
       <c r="F15">
-        <v>90.92200000000001</v>
+        <v>97.91600000000003</v>
       </c>
       <c r="G15">
         <v>166.5</v>
@@ -2654,45 +2654,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M15">
-        <v>5.027986600000001</v>
+        <v>5.659544800000002</v>
       </c>
       <c r="N15">
-        <v>17.9970134</v>
+        <v>17.3654552</v>
       </c>
       <c r="O15">
-        <v>4.139313082000001</v>
+        <v>3.994054696000001</v>
       </c>
       <c r="P15">
-        <v>13.857700318</v>
+        <v>13.371400504</v>
       </c>
       <c r="Q15">
-        <v>78.95770031799999</v>
+        <v>78.471400504</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1335396950309213</v>
+        <v>0.1343494840621864</v>
       </c>
       <c r="T15">
-        <v>1.357305177561531</v>
+        <v>1.36983235633143</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.23</v>
       </c>
       <c r="W15">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.579367812953201</v>
+        <v>4.068348394379703</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2700,22 +2700,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1217713962934803</v>
+        <v>0.1219817279100592</v>
       </c>
       <c r="C16">
-        <v>611.6123839262866</v>
+        <v>603.6520574128283</v>
       </c>
       <c r="D16">
-        <v>543.0283839262867</v>
+        <v>542.0620574128284</v>
       </c>
       <c r="E16">
-        <v>61.71600000000002</v>
+        <v>68.71000000000002</v>
       </c>
       <c r="F16">
-        <v>97.91600000000003</v>
+        <v>104.91</v>
       </c>
       <c r="G16">
         <v>166.5</v>
@@ -2736,45 +2736,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M16">
-        <v>5.659544800000002</v>
+        <v>6.430983000000001</v>
       </c>
       <c r="N16">
-        <v>17.3654552</v>
+        <v>16.594017</v>
       </c>
       <c r="O16">
-        <v>3.994054696000001</v>
+        <v>3.816623910000001</v>
       </c>
       <c r="P16">
-        <v>13.371400504</v>
+        <v>12.77739309</v>
       </c>
       <c r="Q16">
-        <v>78.471400504</v>
+        <v>77.87739309</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1343494840621864</v>
+        <v>0.1351783269530108</v>
       </c>
       <c r="T16">
-        <v>1.36983235633143</v>
+        <v>1.382654292248856</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.23</v>
       </c>
       <c r="W16">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.068348394379703</v>
+        <v>3.580323567952209</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2782,22 +2782,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1219817279100592</v>
+        <v>0.122159719526638</v>
       </c>
       <c r="C17">
-        <v>603.6520574128285</v>
+        <v>595.8429931540785</v>
       </c>
       <c r="D17">
-        <v>542.0620574128285</v>
+        <v>541.2469931540785</v>
       </c>
       <c r="E17">
-        <v>68.71000000000001</v>
+        <v>75.70400000000001</v>
       </c>
       <c r="F17">
-        <v>104.91</v>
+        <v>111.904</v>
       </c>
       <c r="G17">
         <v>166.5</v>
@@ -2818,45 +2818,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M17">
-        <v>6.430983</v>
+        <v>7.173046400000001</v>
       </c>
       <c r="N17">
-        <v>16.594017</v>
+        <v>15.85195360000001</v>
       </c>
       <c r="O17">
-        <v>3.816623910000001</v>
+        <v>3.645949328000001</v>
       </c>
       <c r="P17">
-        <v>12.77739309</v>
+        <v>12.206004272</v>
       </c>
       <c r="Q17">
-        <v>77.87739309</v>
+        <v>77.306004272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1351783269530108</v>
+        <v>0.1360269041983786</v>
       </c>
       <c r="T17">
-        <v>1.382654292248856</v>
+        <v>1.395781512354792</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.23</v>
       </c>
       <c r="W17">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.58032356795221</v>
+        <v>3.209933230042957</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2864,22 +2864,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.122159719526638</v>
+        <v>0.1220143111432168</v>
       </c>
       <c r="C18">
-        <v>595.8429931540785</v>
+        <v>589.5146678402789</v>
       </c>
       <c r="D18">
-        <v>541.2469931540785</v>
+        <v>541.9126678402789</v>
       </c>
       <c r="E18">
-        <v>75.70400000000001</v>
+        <v>82.69800000000002</v>
       </c>
       <c r="F18">
-        <v>111.904</v>
+        <v>118.898</v>
       </c>
       <c r="G18">
         <v>166.5</v>
@@ -2900,28 +2900,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M18">
-        <v>7.173046400000001</v>
+        <v>7.621361800000002</v>
       </c>
       <c r="N18">
-        <v>15.85195360000001</v>
+        <v>15.4036382</v>
       </c>
       <c r="O18">
-        <v>3.645949328000001</v>
+        <v>3.542836786000001</v>
       </c>
       <c r="P18">
-        <v>12.206004272</v>
+        <v>11.860801414</v>
       </c>
       <c r="Q18">
-        <v>77.306004272</v>
+        <v>76.960801414</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1360269041983786</v>
+        <v>0.136895929088213</v>
       </c>
       <c r="T18">
-        <v>1.395781512354792</v>
+        <v>1.409225051017498</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.209933230042957</v>
+        <v>3.021113628275724</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2946,22 +2946,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1220143111432168</v>
+        <v>0.1229499827597957</v>
       </c>
       <c r="C19">
-        <v>589.5146678402789</v>
+        <v>578.2656014068406</v>
       </c>
       <c r="D19">
-        <v>541.9126678402789</v>
+        <v>537.6576014068406</v>
       </c>
       <c r="E19">
-        <v>82.69800000000002</v>
+        <v>89.69200000000002</v>
       </c>
       <c r="F19">
-        <v>118.898</v>
+        <v>125.892</v>
       </c>
       <c r="G19">
         <v>166.5</v>
@@ -2982,45 +2982,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M19">
-        <v>7.621361800000002</v>
+        <v>9.051634800000002</v>
       </c>
       <c r="N19">
-        <v>15.4036382</v>
+        <v>13.9733652</v>
       </c>
       <c r="O19">
-        <v>3.542836786000001</v>
+        <v>3.213873996000001</v>
       </c>
       <c r="P19">
-        <v>11.860801414</v>
+        <v>10.759491204</v>
       </c>
       <c r="Q19">
-        <v>76.960801414</v>
+        <v>75.85949120399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.136895929088213</v>
+        <v>0.1377861497070679</v>
       </c>
       <c r="T19">
-        <v>1.409225051017498</v>
+        <v>1.422996480867098</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.23</v>
       </c>
       <c r="W19">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.021113628275724</v>
+        <v>2.543739391695299</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3028,22 +3028,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1229499827597957</v>
+        <v>0.1234352043763745</v>
       </c>
       <c r="C20">
-        <v>578.2656014068406</v>
+        <v>569.0912087155725</v>
       </c>
       <c r="D20">
-        <v>537.6576014068406</v>
+        <v>535.4772087155726</v>
       </c>
       <c r="E20">
-        <v>89.69200000000001</v>
+        <v>96.68600000000002</v>
       </c>
       <c r="F20">
-        <v>125.892</v>
+        <v>132.886</v>
       </c>
       <c r="G20">
         <v>166.5</v>
@@ -3064,45 +3064,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M20">
-        <v>9.051634800000002</v>
+        <v>10.0727588</v>
       </c>
       <c r="N20">
-        <v>13.9733652</v>
+        <v>12.9522412</v>
       </c>
       <c r="O20">
-        <v>3.213873996000001</v>
+        <v>2.979015476000001</v>
       </c>
       <c r="P20">
-        <v>10.759491204</v>
+        <v>9.973225724000002</v>
       </c>
       <c r="Q20">
-        <v>75.85949120399999</v>
+        <v>75.073225724</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1377861497070679</v>
+        <v>0.1386983510819438</v>
       </c>
       <c r="T20">
-        <v>1.422996480867098</v>
+        <v>1.437107946021627</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.23</v>
       </c>
       <c r="W20">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.543739391695299</v>
+        <v>2.285868296578292</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3110,22 +3110,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1234352043763745</v>
+        <v>0.1233798859929533</v>
       </c>
       <c r="C21">
-        <v>569.0912087155725</v>
+        <v>562.3448939371261</v>
       </c>
       <c r="D21">
-        <v>535.4772087155726</v>
+        <v>535.7248939371261</v>
       </c>
       <c r="E21">
-        <v>96.68600000000002</v>
+        <v>103.68</v>
       </c>
       <c r="F21">
-        <v>132.886</v>
+        <v>139.88</v>
       </c>
       <c r="G21">
         <v>166.5</v>
@@ -3146,28 +3146,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M21">
-        <v>10.0727588</v>
+        <v>10.602904</v>
       </c>
       <c r="N21">
-        <v>12.9522412</v>
+        <v>12.422096</v>
       </c>
       <c r="O21">
-        <v>2.979015476000001</v>
+        <v>2.857082080000001</v>
       </c>
       <c r="P21">
-        <v>9.973225724000002</v>
+        <v>9.565013920000002</v>
       </c>
       <c r="Q21">
-        <v>75.073225724</v>
+        <v>74.66501391999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1386983510819438</v>
+        <v>0.1396333574911917</v>
       </c>
       <c r="T21">
-        <v>1.437107946021627</v>
+        <v>1.45157219780502</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.285868296578292</v>
+        <v>2.171574881749377</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3192,22 +3192,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1233798859929533</v>
+        <v>0.1233245676095322</v>
       </c>
       <c r="C22">
-        <v>562.3448939371261</v>
+        <v>555.5988083985337</v>
       </c>
       <c r="D22">
-        <v>535.7248939371261</v>
+        <v>535.9728083985337</v>
       </c>
       <c r="E22">
-        <v>103.68</v>
+        <v>110.674</v>
       </c>
       <c r="F22">
-        <v>139.88</v>
+        <v>146.874</v>
       </c>
       <c r="G22">
         <v>166.5</v>
@@ -3228,28 +3228,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M22">
-        <v>10.602904</v>
+        <v>11.1330492</v>
       </c>
       <c r="N22">
-        <v>12.422096</v>
+        <v>11.8919508</v>
       </c>
       <c r="O22">
-        <v>2.857082080000001</v>
+        <v>2.735148684000001</v>
       </c>
       <c r="P22">
-        <v>9.565013920000002</v>
+        <v>9.156802116000003</v>
       </c>
       <c r="Q22">
-        <v>74.66501391999999</v>
+        <v>74.256802116</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1396333574911917</v>
+        <v>0.1405920349487749</v>
       </c>
       <c r="T22">
-        <v>1.45157219780502</v>
+        <v>1.466402633177865</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.171574881749377</v>
+        <v>2.068166554047026</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3274,22 +3274,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1233245676095322</v>
+        <v>0.125674729226111</v>
       </c>
       <c r="C23">
-        <v>555.5988083985338</v>
+        <v>538.270639278866</v>
       </c>
       <c r="D23">
-        <v>535.9728083985339</v>
+        <v>525.6386392788661</v>
       </c>
       <c r="E23">
-        <v>110.674</v>
+        <v>117.668</v>
       </c>
       <c r="F23">
-        <v>146.874</v>
+        <v>153.868</v>
       </c>
       <c r="G23">
         <v>166.5</v>
@@ -3310,45 +3310,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M23">
-        <v>11.1330492</v>
+        <v>13.84812</v>
       </c>
       <c r="N23">
-        <v>11.8919508</v>
+        <v>9.176880000000004</v>
       </c>
       <c r="O23">
-        <v>2.735148684000001</v>
+        <v>2.110682400000001</v>
       </c>
       <c r="P23">
-        <v>9.156802116000003</v>
+        <v>7.066197600000003</v>
       </c>
       <c r="Q23">
-        <v>74.256802116</v>
+        <v>72.1661976</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1405920349487749</v>
+        <v>0.1415752938796295</v>
       </c>
       <c r="T23">
-        <v>1.466402633177865</v>
+        <v>1.481613336124373</v>
       </c>
       <c r="U23">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.068166554047026</v>
+        <v>1.662680566026291</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3356,22 +3356,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.125674729226111</v>
+        <v>0.1257287508426898</v>
       </c>
       <c r="C24">
-        <v>538.270639278866</v>
+        <v>531.0437778816374</v>
       </c>
       <c r="D24">
-        <v>525.6386392788661</v>
+        <v>525.4057778816374</v>
       </c>
       <c r="E24">
-        <v>117.668</v>
+        <v>124.662</v>
       </c>
       <c r="F24">
-        <v>153.868</v>
+        <v>160.862</v>
       </c>
       <c r="G24">
         <v>166.5</v>
@@ -3392,28 +3392,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M24">
-        <v>13.84812</v>
+        <v>14.47758</v>
       </c>
       <c r="N24">
-        <v>9.176880000000004</v>
+        <v>8.547420000000004</v>
       </c>
       <c r="O24">
-        <v>2.110682400000001</v>
+        <v>1.965906600000001</v>
       </c>
       <c r="P24">
-        <v>7.066197600000003</v>
+        <v>6.581513400000003</v>
       </c>
       <c r="Q24">
-        <v>72.1661976</v>
+        <v>71.6815134</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1415752938796295</v>
+        <v>0.1425840920034933</v>
       </c>
       <c r="T24">
-        <v>1.481613336124373</v>
+        <v>1.497219122264297</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.662680566026291</v>
+        <v>1.590390106633844</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3438,22 +3438,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1257287508426898</v>
+        <v>0.1257827724592687</v>
       </c>
       <c r="C25">
-        <v>531.0437778816374</v>
+        <v>523.8171227113301</v>
       </c>
       <c r="D25">
-        <v>525.4057778816374</v>
+        <v>525.1731227113301</v>
       </c>
       <c r="E25">
-        <v>124.662</v>
+        <v>131.656</v>
       </c>
       <c r="F25">
-        <v>160.862</v>
+        <v>167.856</v>
       </c>
       <c r="G25">
         <v>166.5</v>
@@ -3474,28 +3474,28 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M25">
-        <v>14.47758</v>
+        <v>15.10704</v>
       </c>
       <c r="N25">
-        <v>8.547420000000004</v>
+        <v>7.917960000000004</v>
       </c>
       <c r="O25">
-        <v>1.965906600000001</v>
+        <v>1.821130800000001</v>
       </c>
       <c r="P25">
-        <v>6.581513400000003</v>
+        <v>6.096829200000004</v>
       </c>
       <c r="Q25">
-        <v>71.6815134</v>
+        <v>71.1968292</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1425840920034933</v>
+        <v>0.1436194374464061</v>
       </c>
       <c r="T25">
-        <v>1.497219122264297</v>
+        <v>1.513235586986851</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.590390106633844</v>
+        <v>1.524123852190767</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3520,22 +3520,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1257827724592687</v>
+        <v>0.1381058212332382</v>
       </c>
       <c r="C26">
-        <v>523.8171227113301</v>
+        <v>468.6417345187275</v>
       </c>
       <c r="D26">
-        <v>525.1731227113301</v>
+        <v>476.9917345187275</v>
       </c>
       <c r="E26">
-        <v>131.656</v>
+        <v>138.65</v>
       </c>
       <c r="F26">
-        <v>167.856</v>
+        <v>174.85</v>
       </c>
       <c r="G26">
         <v>166.5</v>
@@ -3556,45 +3556,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M26">
-        <v>15.10704</v>
+        <v>25.66798000000001</v>
       </c>
       <c r="N26">
-        <v>7.917960000000004</v>
+        <v>-2.642980000000001</v>
       </c>
       <c r="O26">
-        <v>1.821130800000001</v>
+        <v>-0.6078854000000004</v>
       </c>
       <c r="P26">
-        <v>6.096829200000004</v>
+        <v>-2.035094600000001</v>
       </c>
       <c r="Q26">
-        <v>71.1968292</v>
+        <v>63.06490539999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1436194374464061</v>
+        <v>0.1453035580412293</v>
       </c>
       <c r="T26">
-        <v>1.513235586986851</v>
+        <v>1.539288396974233</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.23</v>
+        <v>0.2063173650595022</v>
       </c>
       <c r="W26">
-        <v>0.0693</v>
+        <v>0.1165126108092651</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.524123852190767</v>
+        <v>0.8970320219978354</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3602,22 +3602,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1381058212332382</v>
+        <v>0.1391158212332382</v>
       </c>
       <c r="C27">
-        <v>468.6417345187275</v>
+        <v>458.0878371038584</v>
       </c>
       <c r="D27">
-        <v>476.9917345187275</v>
+        <v>473.4318371038584</v>
       </c>
       <c r="E27">
-        <v>138.65</v>
+        <v>145.644</v>
       </c>
       <c r="F27">
-        <v>174.85</v>
+        <v>181.844</v>
       </c>
       <c r="G27">
         <v>166.5</v>
@@ -3638,37 +3638,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M27">
-        <v>25.66798000000001</v>
+        <v>26.69469920000001</v>
       </c>
       <c r="N27">
-        <v>-2.642980000000001</v>
+        <v>-3.6696992</v>
       </c>
       <c r="O27">
-        <v>-0.6078854000000004</v>
+        <v>-0.8440308160000001</v>
       </c>
       <c r="P27">
-        <v>-2.035094600000001</v>
+        <v>-2.825668384</v>
       </c>
       <c r="Q27">
-        <v>63.06490539999999</v>
+        <v>62.274331616</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1453035580412293</v>
+        <v>0.1466482007174621</v>
       </c>
       <c r="T27">
-        <v>1.539288396974233</v>
+        <v>1.560089591527938</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2063173650595022</v>
+        <v>0.1983820817879829</v>
       </c>
       <c r="W27">
-        <v>0.1165126108092651</v>
+        <v>0.1176775103935241</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8970320219978354</v>
+        <v>0.8625307903825341</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1391158212332382</v>
+        <v>0.1401258212332382</v>
       </c>
       <c r="C28">
-        <v>458.0878371038584</v>
+        <v>447.5866826983237</v>
       </c>
       <c r="D28">
-        <v>473.4318371038584</v>
+        <v>469.9246826983238</v>
       </c>
       <c r="E28">
-        <v>145.644</v>
+        <v>152.638</v>
       </c>
       <c r="F28">
-        <v>181.844</v>
+        <v>188.8380000000001</v>
       </c>
       <c r="G28">
         <v>166.5</v>
@@ -3720,37 +3720,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M28">
-        <v>26.69469920000001</v>
+        <v>27.72141840000001</v>
       </c>
       <c r="N28">
-        <v>-3.6696992</v>
+        <v>-4.696418400000006</v>
       </c>
       <c r="O28">
-        <v>-0.8440308160000001</v>
+        <v>-1.080176232000001</v>
       </c>
       <c r="P28">
-        <v>-2.825668384</v>
+        <v>-3.616242168000005</v>
       </c>
       <c r="Q28">
-        <v>62.274331616</v>
+        <v>61.48375783199999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1466482007174621</v>
+        <v>0.1480296829190712</v>
       </c>
       <c r="T28">
-        <v>1.560089591527938</v>
+        <v>1.581460681822842</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.1983820817879829</v>
+        <v>0.1910345972773168</v>
       </c>
       <c r="W28">
-        <v>0.1176775103935241</v>
+        <v>0.1187561211196899</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8625307903825341</v>
+        <v>0.8305852055535512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3766,22 +3766,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1401258212332382</v>
+        <v>0.1411358212332382</v>
       </c>
       <c r="C29">
-        <v>447.5866826983237</v>
+        <v>437.1371077704299</v>
       </c>
       <c r="D29">
-        <v>469.9246826983238</v>
+        <v>466.4691077704299</v>
       </c>
       <c r="E29">
-        <v>152.638</v>
+        <v>159.6320000000001</v>
       </c>
       <c r="F29">
-        <v>188.8380000000001</v>
+        <v>195.8320000000001</v>
       </c>
       <c r="G29">
         <v>166.5</v>
@@ -3802,37 +3802,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M29">
-        <v>27.72141840000001</v>
+        <v>28.74813760000001</v>
       </c>
       <c r="N29">
-        <v>-4.696418400000006</v>
+        <v>-5.723137600000005</v>
       </c>
       <c r="O29">
-        <v>-1.080176232000001</v>
+        <v>-1.316321648000001</v>
       </c>
       <c r="P29">
-        <v>-3.616242168000005</v>
+        <v>-4.406815952000004</v>
       </c>
       <c r="Q29">
-        <v>61.48375783199999</v>
+        <v>60.69318404799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1480296829190712</v>
+        <v>0.1494495396262805</v>
       </c>
       <c r="T29">
-        <v>1.581460681822842</v>
+        <v>1.603425413514826</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.1910345972773168</v>
+        <v>0.1842119330888412</v>
       </c>
       <c r="W29">
-        <v>0.1187561211196899</v>
+        <v>0.1197576882225581</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8305852055535512</v>
+        <v>0.800921448212353</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3848,22 +3848,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1411358212332382</v>
+        <v>0.1588972734097549</v>
       </c>
       <c r="C30">
-        <v>437.1371077704299</v>
+        <v>376.728884582318</v>
       </c>
       <c r="D30">
-        <v>466.4691077704299</v>
+        <v>413.0548845823179</v>
       </c>
       <c r="E30">
-        <v>159.6320000000001</v>
+        <v>166.626</v>
       </c>
       <c r="F30">
-        <v>195.8320000000001</v>
+        <v>202.8260000000001</v>
       </c>
       <c r="G30">
         <v>166.5</v>
@@ -3884,45 +3884,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M30">
-        <v>28.74813760000001</v>
+        <v>40.72746080000001</v>
       </c>
       <c r="N30">
-        <v>-5.723137600000005</v>
+        <v>-17.7024608</v>
       </c>
       <c r="O30">
-        <v>-1.316321648000001</v>
+        <v>-4.071565984000001</v>
       </c>
       <c r="P30">
-        <v>-4.406815952000004</v>
+        <v>-13.630894816</v>
       </c>
       <c r="Q30">
-        <v>60.69318404799999</v>
+        <v>51.46910518399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1494495396262805</v>
+        <v>0.1524466488837164</v>
       </c>
       <c r="T30">
-        <v>1.603425413514826</v>
+        <v>1.649789740532394</v>
       </c>
       <c r="U30">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1842119330888412</v>
+        <v>0.1300289754376242</v>
       </c>
       <c r="W30">
-        <v>0.1197576882225581</v>
+        <v>0.1746901817321251</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.800921448212353</v>
+        <v>0.565343371467931</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3930,22 +3930,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1588972734097549</v>
+        <v>0.1604472734097549</v>
       </c>
       <c r="C31">
-        <v>376.728884582318</v>
+        <v>365.6481471062756</v>
       </c>
       <c r="D31">
-        <v>413.0548845823179</v>
+        <v>408.9681471062756</v>
       </c>
       <c r="E31">
-        <v>166.626</v>
+        <v>173.62</v>
       </c>
       <c r="F31">
-        <v>202.826</v>
+        <v>209.82</v>
       </c>
       <c r="G31">
         <v>166.5</v>
@@ -3966,37 +3966,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M31">
-        <v>40.7274608</v>
+        <v>42.13185600000001</v>
       </c>
       <c r="N31">
-        <v>-17.7024608</v>
+        <v>-19.106856</v>
       </c>
       <c r="O31">
-        <v>-4.071565983999999</v>
+        <v>-4.394576880000001</v>
       </c>
       <c r="P31">
-        <v>-13.630894816</v>
+        <v>-14.71227912</v>
       </c>
       <c r="Q31">
-        <v>51.469105184</v>
+        <v>50.38772088</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1524466488837164</v>
+        <v>0.1539701724391981</v>
       </c>
       <c r="T31">
-        <v>1.649789740532394</v>
+        <v>1.673358165397143</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1300289754376242</v>
+        <v>0.12569467625637</v>
       </c>
       <c r="W31">
-        <v>0.1746901817321251</v>
+        <v>0.1755605090077209</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5653433714679311</v>
+        <v>0.546498592419</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4012,22 +4012,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1604472734097549</v>
+        <v>0.1619972734097549</v>
       </c>
       <c r="C32">
-        <v>365.6481471062756</v>
+        <v>354.6474851840257</v>
       </c>
       <c r="D32">
-        <v>408.9681471062756</v>
+        <v>404.9614851840257</v>
       </c>
       <c r="E32">
-        <v>173.62</v>
+        <v>180.614</v>
       </c>
       <c r="F32">
-        <v>209.82</v>
+        <v>216.814</v>
       </c>
       <c r="G32">
         <v>166.5</v>
@@ -4048,37 +4048,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M32">
-        <v>42.13185600000001</v>
+        <v>43.5362512</v>
       </c>
       <c r="N32">
-        <v>-19.106856</v>
+        <v>-20.5112512</v>
       </c>
       <c r="O32">
-        <v>-4.394576880000001</v>
+        <v>-4.717587775999999</v>
       </c>
       <c r="P32">
-        <v>-14.71227912</v>
+        <v>-15.793663424</v>
       </c>
       <c r="Q32">
-        <v>50.38772088</v>
+        <v>49.30633657599999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1539701724391981</v>
+        <v>0.1555378560977372</v>
       </c>
       <c r="T32">
-        <v>1.673358165397143</v>
+        <v>1.697609733011594</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.12569467625637</v>
+        <v>0.1216400092803581</v>
       </c>
       <c r="W32">
-        <v>0.1755605090077209</v>
+        <v>0.1763746861365041</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.546498592419</v>
+        <v>0.5288696055667743</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4094,22 +4094,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1619972734097549</v>
+        <v>0.1635472734097549</v>
       </c>
       <c r="C33">
-        <v>354.6474851840257</v>
+        <v>343.7245681479443</v>
       </c>
       <c r="D33">
-        <v>404.9614851840257</v>
+        <v>401.0325681479443</v>
       </c>
       <c r="E33">
-        <v>180.614</v>
+        <v>187.608</v>
       </c>
       <c r="F33">
-        <v>216.814</v>
+        <v>223.808</v>
       </c>
       <c r="G33">
         <v>166.5</v>
@@ -4130,37 +4130,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M33">
-        <v>43.5362512</v>
+        <v>44.94064640000001</v>
       </c>
       <c r="N33">
-        <v>-20.5112512</v>
+        <v>-21.9156464</v>
       </c>
       <c r="O33">
-        <v>-4.717587775999999</v>
+        <v>-5.040598672</v>
       </c>
       <c r="P33">
-        <v>-15.793663424</v>
+        <v>-16.875047728</v>
       </c>
       <c r="Q33">
-        <v>49.30633657599999</v>
+        <v>48.224952272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1555378560977372</v>
+        <v>0.1571516480991745</v>
       </c>
       <c r="T33">
-        <v>1.697609733011594</v>
+        <v>1.722574582026471</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1216400092803581</v>
+        <v>0.1178387589903469</v>
       </c>
       <c r="W33">
-        <v>0.1763746861365041</v>
+        <v>0.1771379771947383</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5288696055667743</v>
+        <v>0.5123424303928126</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1635472734097549</v>
+        <v>0.1770876875462597</v>
       </c>
       <c r="C34">
-        <v>343.7245681479443</v>
+        <v>305.3971457000256</v>
       </c>
       <c r="D34">
-        <v>401.0325681479443</v>
+        <v>369.6991457000257</v>
       </c>
       <c r="E34">
-        <v>187.608</v>
+        <v>194.602</v>
       </c>
       <c r="F34">
-        <v>223.808</v>
+        <v>230.802</v>
       </c>
       <c r="G34">
         <v>166.5</v>
@@ -4212,45 +4212,45 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M34">
-        <v>44.94064640000001</v>
+        <v>54.42311160000001</v>
       </c>
       <c r="N34">
-        <v>-21.9156464</v>
+        <v>-31.39811160000001</v>
       </c>
       <c r="O34">
-        <v>-5.040598672</v>
+        <v>-7.221565668000002</v>
       </c>
       <c r="P34">
-        <v>-16.875047728</v>
+        <v>-24.176545932</v>
       </c>
       <c r="Q34">
-        <v>48.224952272</v>
+        <v>40.92345406799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1571516480991745</v>
+        <v>0.1594709475282738</v>
       </c>
       <c r="T34">
-        <v>1.722574582026471</v>
+        <v>1.758453406569029</v>
       </c>
       <c r="U34">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1178387589903469</v>
+        <v>0.0973070051363987</v>
       </c>
       <c r="W34">
-        <v>0.1771379771947383</v>
+        <v>0.2128550081888372</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.5123424303928126</v>
+        <v>0.4230739353756465</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4258,22 +4258,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1770876875462597</v>
+        <v>0.1789876875462597</v>
       </c>
       <c r="C35">
-        <v>305.3971457000256</v>
+        <v>294.3938987429964</v>
       </c>
       <c r="D35">
-        <v>369.6991457000257</v>
+        <v>365.6898987429964</v>
       </c>
       <c r="E35">
-        <v>194.602</v>
+        <v>201.5960000000001</v>
       </c>
       <c r="F35">
-        <v>230.802</v>
+        <v>237.796</v>
       </c>
       <c r="G35">
         <v>166.5</v>
@@ -4294,37 +4294,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M35">
-        <v>54.42311160000001</v>
+        <v>56.07229680000001</v>
       </c>
       <c r="N35">
-        <v>-31.39811160000001</v>
+        <v>-33.04729680000001</v>
       </c>
       <c r="O35">
-        <v>-7.221565668000002</v>
+        <v>-7.600878264000001</v>
       </c>
       <c r="P35">
-        <v>-24.176545932</v>
+        <v>-25.446418536</v>
       </c>
       <c r="Q35">
-        <v>40.92345406799999</v>
+        <v>39.65358146399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1594709475282738</v>
+        <v>0.1611932346120355</v>
       </c>
       <c r="T35">
-        <v>1.758453406569029</v>
+        <v>1.785096640001893</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0973070051363987</v>
+        <v>0.09444503439709287</v>
       </c>
       <c r="W35">
-        <v>0.2128550081888372</v>
+        <v>0.2135298608891655</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4230739353756465</v>
+        <v>0.4106305843351864</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4340,22 +4340,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1789876875462597</v>
+        <v>0.1808876875462597</v>
       </c>
       <c r="C36">
-        <v>294.3938987429964</v>
+        <v>283.4766764055811</v>
       </c>
       <c r="D36">
-        <v>365.6898987429964</v>
+        <v>361.7666764055812</v>
       </c>
       <c r="E36">
-        <v>201.5960000000001</v>
+        <v>208.59</v>
       </c>
       <c r="F36">
-        <v>237.796</v>
+        <v>244.79</v>
       </c>
       <c r="G36">
         <v>166.5</v>
@@ -4376,37 +4376,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M36">
-        <v>56.07229680000001</v>
+        <v>57.72148200000002</v>
       </c>
       <c r="N36">
-        <v>-33.04729680000001</v>
+        <v>-34.69648200000001</v>
       </c>
       <c r="O36">
-        <v>-7.600878264000001</v>
+        <v>-7.980190860000003</v>
       </c>
       <c r="P36">
-        <v>-25.446418536</v>
+        <v>-26.71629114000001</v>
       </c>
       <c r="Q36">
-        <v>39.65358146399999</v>
+        <v>38.38370885999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1611932346120355</v>
+        <v>0.1629685151445284</v>
       </c>
       <c r="T36">
-        <v>1.785096640001893</v>
+        <v>1.812559665232691</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.09444503439709287</v>
+        <v>0.09174660484289021</v>
       </c>
       <c r="W36">
-        <v>0.2135298608891655</v>
+        <v>0.2141661505780465</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4106305843351864</v>
+        <v>0.3988982819256096</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4422,22 +4422,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1808876875462597</v>
+        <v>0.1827876875462597</v>
       </c>
       <c r="C37">
-        <v>283.4766764055811</v>
+        <v>272.6427393880367</v>
       </c>
       <c r="D37">
-        <v>361.7666764055812</v>
+        <v>357.9267393880367</v>
       </c>
       <c r="E37">
-        <v>208.59</v>
+        <v>215.5840000000001</v>
       </c>
       <c r="F37">
-        <v>244.79</v>
+        <v>251.784</v>
       </c>
       <c r="G37">
         <v>166.5</v>
@@ -4458,37 +4458,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M37">
-        <v>57.72148200000002</v>
+        <v>59.37066720000001</v>
       </c>
       <c r="N37">
-        <v>-34.69648200000001</v>
+        <v>-36.34566720000001</v>
       </c>
       <c r="O37">
-        <v>-7.980190860000003</v>
+        <v>-8.359503456000002</v>
       </c>
       <c r="P37">
-        <v>-26.71629114000001</v>
+        <v>-27.98616374400001</v>
       </c>
       <c r="Q37">
-        <v>38.38370885999998</v>
+        <v>37.11383625599998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1629685151445284</v>
+        <v>0.1647992731936616</v>
       </c>
       <c r="T37">
-        <v>1.812559665232691</v>
+        <v>1.840880910001952</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.09174660484289021</v>
+        <v>0.08919808804169882</v>
       </c>
       <c r="W37">
-        <v>0.2141661505780465</v>
+        <v>0.2147670908397674</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3988982819256096</v>
+        <v>0.3878177740943427</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4504,22 +4504,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1827876875462597</v>
+        <v>0.1846876875462597</v>
       </c>
       <c r="C38">
-        <v>272.6427393880366</v>
+        <v>261.8894634732038</v>
       </c>
       <c r="D38">
-        <v>357.9267393880367</v>
+        <v>354.1674634732038</v>
       </c>
       <c r="E38">
-        <v>215.584</v>
+        <v>222.578</v>
       </c>
       <c r="F38">
-        <v>251.784</v>
+        <v>258.778</v>
       </c>
       <c r="G38">
         <v>166.5</v>
@@ -4540,37 +4540,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M38">
-        <v>59.37066720000001</v>
+        <v>61.0198524</v>
       </c>
       <c r="N38">
-        <v>-36.3456672</v>
+        <v>-37.9948524</v>
       </c>
       <c r="O38">
-        <v>-8.359503456000001</v>
+        <v>-8.738816052000001</v>
       </c>
       <c r="P38">
-        <v>-27.986163744</v>
+        <v>-29.256036348</v>
       </c>
       <c r="Q38">
-        <v>37.11383625599999</v>
+        <v>35.843963652</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1647992731936616</v>
+        <v>0.166688150545942</v>
       </c>
       <c r="T38">
-        <v>1.840880910001952</v>
+        <v>1.870101241906745</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08919808804169882</v>
+        <v>0.08678732890543669</v>
       </c>
       <c r="W38">
-        <v>0.2147670908397674</v>
+        <v>0.215335547844098</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3878177740943427</v>
+        <v>0.3773362126323335</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4586,22 +4586,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1846876875462597</v>
+        <v>0.1865876875462597</v>
       </c>
       <c r="C39">
-        <v>261.8894634732038</v>
+        <v>251.2143335458072</v>
       </c>
       <c r="D39">
-        <v>354.1674634732038</v>
+        <v>350.4863335458073</v>
       </c>
       <c r="E39">
-        <v>222.578</v>
+        <v>229.5720000000001</v>
       </c>
       <c r="F39">
-        <v>258.778</v>
+        <v>265.772</v>
       </c>
       <c r="G39">
         <v>166.5</v>
@@ -4622,37 +4622,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M39">
-        <v>61.0198524</v>
+        <v>62.66903760000002</v>
       </c>
       <c r="N39">
-        <v>-37.9948524</v>
+        <v>-39.64403760000001</v>
       </c>
       <c r="O39">
-        <v>-8.738816052000001</v>
+        <v>-9.118128648000003</v>
       </c>
       <c r="P39">
-        <v>-29.256036348</v>
+        <v>-30.52590895200001</v>
       </c>
       <c r="Q39">
-        <v>35.843963652</v>
+        <v>34.57409104799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.166688150545942</v>
+        <v>0.1686379594257152</v>
       </c>
       <c r="T39">
-        <v>1.870101241906745</v>
+        <v>1.900264165163305</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08678732890543669</v>
+        <v>0.08450345182897782</v>
       </c>
       <c r="W39">
-        <v>0.215335547844098</v>
+        <v>0.215874086058727</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3773362126323335</v>
+        <v>0.3674063122999036</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1865876875462597</v>
+        <v>0.1884876875462597</v>
       </c>
       <c r="C40">
-        <v>251.2143335458072</v>
+        <v>240.6149379808883</v>
       </c>
       <c r="D40">
-        <v>350.4863335458073</v>
+        <v>346.8809379808884</v>
       </c>
       <c r="E40">
-        <v>229.5720000000001</v>
+        <v>236.566</v>
       </c>
       <c r="F40">
-        <v>265.772</v>
+        <v>272.766</v>
       </c>
       <c r="G40">
         <v>166.5</v>
@@ -4704,37 +4704,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M40">
-        <v>62.66903760000002</v>
+        <v>64.3182228</v>
       </c>
       <c r="N40">
-        <v>-39.64403760000001</v>
+        <v>-41.2932228</v>
       </c>
       <c r="O40">
-        <v>-9.118128648000003</v>
+        <v>-9.497441243999999</v>
       </c>
       <c r="P40">
-        <v>-30.52590895200001</v>
+        <v>-31.79578155599999</v>
       </c>
       <c r="Q40">
-        <v>34.57409104799999</v>
+        <v>33.304218444</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1686379594257152</v>
+        <v>0.1706516964654811</v>
       </c>
       <c r="T40">
-        <v>1.900264165163305</v>
+        <v>1.93141603672336</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08450345182897782</v>
+        <v>0.08233669665387584</v>
       </c>
       <c r="W40">
-        <v>0.215874086058727</v>
+        <v>0.2163850069290161</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3674063122999036</v>
+        <v>0.3579856376255471</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1884876875462597</v>
+        <v>0.1903876875462597</v>
       </c>
       <c r="C41">
-        <v>240.6149379808883</v>
+        <v>230.0889633750648</v>
       </c>
       <c r="D41">
-        <v>346.8809379808884</v>
+        <v>343.3489633750648</v>
       </c>
       <c r="E41">
-        <v>236.566</v>
+        <v>243.5600000000001</v>
       </c>
       <c r="F41">
-        <v>272.766</v>
+        <v>279.76</v>
       </c>
       <c r="G41">
         <v>166.5</v>
@@ -4786,37 +4786,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M41">
-        <v>64.3182228</v>
+        <v>65.96740800000002</v>
       </c>
       <c r="N41">
-        <v>-41.2932228</v>
+        <v>-42.94240800000001</v>
       </c>
       <c r="O41">
-        <v>-9.497441243999999</v>
+        <v>-9.876753840000005</v>
       </c>
       <c r="P41">
-        <v>-31.79578155599999</v>
+        <v>-33.06565416000001</v>
       </c>
       <c r="Q41">
-        <v>33.304218444</v>
+        <v>32.03434583999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1706516964654811</v>
+        <v>0.1727325580732391</v>
       </c>
       <c r="T41">
-        <v>1.93141603672336</v>
+        <v>1.963606304002083</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08233669665387584</v>
+        <v>0.08027827923752892</v>
       </c>
       <c r="W41">
-        <v>0.2163850069290161</v>
+        <v>0.2168703817557907</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3579856376255471</v>
+        <v>0.3490359966849084</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4832,22 +4832,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1903876875462597</v>
+        <v>0.1922876875462597</v>
       </c>
       <c r="C42">
-        <v>230.0889633750648</v>
+        <v>219.6341895964259</v>
       </c>
       <c r="D42">
-        <v>343.3489633750648</v>
+        <v>339.888189596426</v>
       </c>
       <c r="E42">
-        <v>243.5600000000001</v>
+        <v>250.5540000000001</v>
       </c>
       <c r="F42">
-        <v>279.76</v>
+        <v>286.7540000000001</v>
       </c>
       <c r="G42">
         <v>166.5</v>
@@ -4868,37 +4868,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M42">
-        <v>65.96740800000002</v>
+        <v>67.61659320000003</v>
       </c>
       <c r="N42">
-        <v>-42.94240800000001</v>
+        <v>-44.59159320000002</v>
       </c>
       <c r="O42">
-        <v>-9.876753840000005</v>
+        <v>-10.256066436</v>
       </c>
       <c r="P42">
-        <v>-33.06565416000001</v>
+        <v>-34.33552676400002</v>
       </c>
       <c r="Q42">
-        <v>32.03434583999999</v>
+        <v>30.76447323599998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1727325580732391</v>
+        <v>0.174883957362616</v>
       </c>
       <c r="T42">
-        <v>1.963606304002083</v>
+        <v>1.996887766781779</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08027827923752892</v>
+        <v>0.07832027242685749</v>
       </c>
       <c r="W42">
-        <v>0.2168703817557907</v>
+        <v>0.217332079761747</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3490359966849084</v>
+        <v>0.3405229235950326</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4914,22 +4914,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1922876875462597</v>
+        <v>0.1941876875462597</v>
       </c>
       <c r="C43">
-        <v>219.6341895964259</v>
+        <v>209.2484851308072</v>
       </c>
       <c r="D43">
-        <v>339.888189596426</v>
+        <v>336.4964851308072</v>
       </c>
       <c r="E43">
-        <v>250.5540000000001</v>
+        <v>257.5480000000001</v>
       </c>
       <c r="F43">
-        <v>286.7540000000001</v>
+        <v>293.748</v>
       </c>
       <c r="G43">
         <v>166.5</v>
@@ -4950,37 +4950,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M43">
-        <v>67.61659320000003</v>
+        <v>69.26577840000002</v>
       </c>
       <c r="N43">
-        <v>-44.59159320000002</v>
+        <v>-46.24077840000001</v>
       </c>
       <c r="O43">
-        <v>-10.256066436</v>
+        <v>-10.635379032</v>
       </c>
       <c r="P43">
-        <v>-34.33552676400002</v>
+        <v>-35.60539936800001</v>
       </c>
       <c r="Q43">
-        <v>30.76447323599998</v>
+        <v>29.49460063199999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.174883957362616</v>
+        <v>0.1771095428343853</v>
       </c>
       <c r="T43">
-        <v>1.996887766781779</v>
+        <v>2.031316866209051</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07832027242685749</v>
+        <v>0.07645550403574185</v>
       </c>
       <c r="W43">
-        <v>0.217332079761747</v>
+        <v>0.2177717921483721</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3405229235950326</v>
+        <v>0.332415234938008</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4996,22 +4996,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1941876875462597</v>
+        <v>0.1960876875462597</v>
       </c>
       <c r="C44">
-        <v>209.2484851308072</v>
+        <v>198.9298027039449</v>
       </c>
       <c r="D44">
-        <v>336.4964851308072</v>
+        <v>333.1718027039449</v>
       </c>
       <c r="E44">
-        <v>257.5480000000001</v>
+        <v>264.542</v>
       </c>
       <c r="F44">
-        <v>293.748</v>
+        <v>300.742</v>
       </c>
       <c r="G44">
         <v>166.5</v>
@@ -5032,37 +5032,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M44">
-        <v>69.26577840000002</v>
+        <v>70.91496360000001</v>
       </c>
       <c r="N44">
-        <v>-46.24077840000001</v>
+        <v>-47.8899636</v>
       </c>
       <c r="O44">
-        <v>-10.635379032</v>
+        <v>-11.014691628</v>
       </c>
       <c r="P44">
-        <v>-35.60539936800001</v>
+        <v>-36.875271972</v>
       </c>
       <c r="Q44">
-        <v>29.49460063199999</v>
+        <v>28.22472802799999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1771095428343853</v>
+        <v>0.1794132190244622</v>
       </c>
       <c r="T44">
-        <v>2.031316866209051</v>
+        <v>2.066954004212718</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07645550403574185</v>
+        <v>0.07467746905816647</v>
       </c>
       <c r="W44">
-        <v>0.2177717921483721</v>
+        <v>0.2181910527960844</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.332415234938008</v>
+        <v>0.3246846480789846</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5078,22 +5078,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1960876875462597</v>
+        <v>0.1979876875462597</v>
       </c>
       <c r="C45">
-        <v>198.9298027039449</v>
+        <v>188.6761751606201</v>
       </c>
       <c r="D45">
-        <v>333.1718027039449</v>
+        <v>329.9121751606201</v>
       </c>
       <c r="E45">
-        <v>264.542</v>
+        <v>271.5360000000001</v>
       </c>
       <c r="F45">
-        <v>300.742</v>
+        <v>307.736</v>
       </c>
       <c r="G45">
         <v>166.5</v>
@@ -5114,37 +5114,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M45">
-        <v>70.91496360000001</v>
+        <v>72.56414880000001</v>
       </c>
       <c r="N45">
-        <v>-47.8899636</v>
+        <v>-49.53914880000001</v>
       </c>
       <c r="O45">
-        <v>-11.014691628</v>
+        <v>-11.394004224</v>
       </c>
       <c r="P45">
-        <v>-36.875271972</v>
+        <v>-38.14514457600001</v>
       </c>
       <c r="Q45">
-        <v>28.22472802799999</v>
+        <v>26.95485542399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1794132190244622</v>
+        <v>0.1817991693641847</v>
       </c>
       <c r="T45">
-        <v>2.066954004212718</v>
+        <v>2.103863897145088</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07467746905816647</v>
+        <v>0.07298025385229905</v>
       </c>
       <c r="W45">
-        <v>0.2181910527960844</v>
+        <v>0.2185912561416279</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3246846480789846</v>
+        <v>0.3173054515317349</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5160,22 +5160,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1979876875462597</v>
+        <v>0.1998876875462597</v>
       </c>
       <c r="C46">
-        <v>188.6761751606201</v>
+        <v>178.4857115833573</v>
       </c>
       <c r="D46">
-        <v>329.9121751606201</v>
+        <v>326.7157115833573</v>
       </c>
       <c r="E46">
-        <v>271.5360000000001</v>
+        <v>278.5300000000001</v>
       </c>
       <c r="F46">
-        <v>307.736</v>
+        <v>314.7300000000001</v>
       </c>
       <c r="G46">
         <v>166.5</v>
@@ -5196,37 +5196,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M46">
-        <v>72.56414880000001</v>
+        <v>74.21333400000002</v>
       </c>
       <c r="N46">
-        <v>-49.53914880000001</v>
+        <v>-51.18833400000001</v>
       </c>
       <c r="O46">
-        <v>-11.394004224</v>
+        <v>-11.77331682</v>
       </c>
       <c r="P46">
-        <v>-38.14514457600001</v>
+        <v>-39.41501718000001</v>
       </c>
       <c r="Q46">
-        <v>26.95485542399999</v>
+        <v>25.68498281999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1817991693641847</v>
+        <v>0.1842718815344426</v>
       </c>
       <c r="T46">
-        <v>2.103863897145088</v>
+        <v>2.142115968002271</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07298025385229905</v>
+        <v>0.07135847043335905</v>
       </c>
       <c r="W46">
-        <v>0.2185912561416279</v>
+        <v>0.2189736726718139</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3173054515317349</v>
+        <v>0.3102542192754741</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5242,22 +5242,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1998876875462597</v>
+        <v>0.2017876875462597</v>
       </c>
       <c r="C47">
-        <v>178.4857115833573</v>
+        <v>168.3565936345927</v>
       </c>
       <c r="D47">
-        <v>326.7157115833573</v>
+        <v>323.5805936345928</v>
       </c>
       <c r="E47">
-        <v>278.5300000000001</v>
+        <v>285.5240000000001</v>
       </c>
       <c r="F47">
-        <v>314.7300000000001</v>
+        <v>321.724</v>
       </c>
       <c r="G47">
         <v>166.5</v>
@@ -5278,37 +5278,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M47">
-        <v>74.21333400000002</v>
+        <v>75.86251920000001</v>
       </c>
       <c r="N47">
-        <v>-51.18833400000001</v>
+        <v>-52.8375192</v>
       </c>
       <c r="O47">
-        <v>-11.77331682</v>
+        <v>-12.152629416</v>
       </c>
       <c r="P47">
-        <v>-39.41501718000001</v>
+        <v>-40.684889784</v>
       </c>
       <c r="Q47">
-        <v>25.68498281999999</v>
+        <v>24.415110216</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1842718815344426</v>
+        <v>0.1868361756369323</v>
       </c>
       <c r="T47">
-        <v>2.142115968002271</v>
+        <v>2.181784782224536</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07135847043335905</v>
+        <v>0.06980719933698169</v>
       </c>
       <c r="W47">
-        <v>0.2189736726718139</v>
+        <v>0.2193394623963397</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3102542192754741</v>
+        <v>0.3035095623347031</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5324,22 +5324,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2017876875462597</v>
+        <v>0.2036876875462597</v>
       </c>
       <c r="C48">
-        <v>168.3565936345927</v>
+        <v>158.2870721074385</v>
       </c>
       <c r="D48">
-        <v>323.5805936345928</v>
+        <v>320.5050721074386</v>
       </c>
       <c r="E48">
-        <v>285.5240000000001</v>
+        <v>292.5180000000001</v>
       </c>
       <c r="F48">
-        <v>321.724</v>
+        <v>328.7180000000001</v>
       </c>
       <c r="G48">
         <v>166.5</v>
@@ -5360,37 +5360,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M48">
-        <v>75.86251920000001</v>
+        <v>77.51170440000003</v>
       </c>
       <c r="N48">
-        <v>-52.8375192</v>
+        <v>-54.48670440000002</v>
       </c>
       <c r="O48">
-        <v>-12.152629416</v>
+        <v>-12.53194201200001</v>
       </c>
       <c r="P48">
-        <v>-40.684889784</v>
+        <v>-41.95476238800002</v>
       </c>
       <c r="Q48">
-        <v>24.415110216</v>
+        <v>23.14523761199997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1868361756369323</v>
+        <v>0.1894972355546103</v>
       </c>
       <c r="T48">
-        <v>2.181784782224536</v>
+        <v>2.222950532832546</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06980719933698169</v>
+        <v>0.06832193977662036</v>
       </c>
       <c r="W48">
-        <v>0.2193394623963397</v>
+        <v>0.2196896866006729</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3035095623347031</v>
+        <v>0.2970519120722624</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5406,22 +5406,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2036876875462597</v>
+        <v>0.2055876875462597</v>
       </c>
       <c r="C49">
-        <v>158.2870721074385</v>
+        <v>148.2754636712994</v>
       </c>
       <c r="D49">
-        <v>320.5050721074386</v>
+        <v>317.4874636712995</v>
       </c>
       <c r="E49">
-        <v>292.5180000000001</v>
+        <v>299.5120000000001</v>
       </c>
       <c r="F49">
-        <v>328.7180000000001</v>
+        <v>335.712</v>
       </c>
       <c r="G49">
         <v>166.5</v>
@@ -5442,37 +5442,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M49">
-        <v>77.51170440000003</v>
+        <v>79.16088960000002</v>
       </c>
       <c r="N49">
-        <v>-54.48670440000002</v>
+        <v>-56.13588960000001</v>
       </c>
       <c r="O49">
-        <v>-12.53194201200001</v>
+        <v>-12.911254608</v>
       </c>
       <c r="P49">
-        <v>-41.95476238800002</v>
+        <v>-43.22463499200001</v>
       </c>
       <c r="Q49">
-        <v>23.14523761199997</v>
+        <v>21.87536500799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1894972355546103</v>
+        <v>0.1922606439306605</v>
       </c>
       <c r="T49">
-        <v>2.222950532832546</v>
+        <v>2.265699581540864</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06832193977662036</v>
+        <v>0.06689856603127411</v>
       </c>
       <c r="W49">
-        <v>0.2196896866006729</v>
+        <v>0.2200253181298256</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2970519120722624</v>
+        <v>0.290863330570757</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5488,22 +5488,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2055876875462597</v>
+        <v>0.2074876875462597</v>
       </c>
       <c r="C50">
-        <v>148.2754636712994</v>
+        <v>138.320147799617</v>
       </c>
       <c r="D50">
-        <v>317.4874636712995</v>
+        <v>314.526147799617</v>
       </c>
       <c r="E50">
-        <v>299.5120000000001</v>
+        <v>306.506</v>
       </c>
       <c r="F50">
-        <v>335.712</v>
+        <v>342.706</v>
       </c>
       <c r="G50">
         <v>166.5</v>
@@ -5524,37 +5524,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M50">
-        <v>79.16088960000002</v>
+        <v>80.81007480000001</v>
       </c>
       <c r="N50">
-        <v>-56.13588960000001</v>
+        <v>-57.7850748</v>
       </c>
       <c r="O50">
-        <v>-12.911254608</v>
+        <v>-13.290567204</v>
       </c>
       <c r="P50">
-        <v>-43.22463499200001</v>
+        <v>-44.49450759600001</v>
       </c>
       <c r="Q50">
-        <v>21.87536500799999</v>
+        <v>20.60549240399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1922606439306605</v>
+        <v>0.1951324212626342</v>
       </c>
       <c r="T50">
-        <v>2.265699581540864</v>
+        <v>2.310125063531862</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06689856603127411</v>
+        <v>0.06553328917349302</v>
       </c>
       <c r="W50">
-        <v>0.2200253181298256</v>
+        <v>0.2203472504128904</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.290863330570757</v>
+        <v>0.2849273442325784</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5570,22 +5570,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2074876875462597</v>
+        <v>0.2093876875462597</v>
       </c>
       <c r="C51">
-        <v>138.320147799617</v>
+        <v>128.4195638679618</v>
       </c>
       <c r="D51">
-        <v>314.526147799617</v>
+        <v>311.6195638679619</v>
       </c>
       <c r="E51">
-        <v>306.506</v>
+        <v>313.5000000000001</v>
       </c>
       <c r="F51">
-        <v>342.706</v>
+        <v>349.7</v>
       </c>
       <c r="G51">
         <v>166.5</v>
@@ -5606,37 +5606,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M51">
-        <v>80.81007480000001</v>
+        <v>82.45926000000001</v>
       </c>
       <c r="N51">
-        <v>-57.7850748</v>
+        <v>-59.43426000000001</v>
       </c>
       <c r="O51">
-        <v>-13.290567204</v>
+        <v>-13.6698798</v>
       </c>
       <c r="P51">
-        <v>-44.49450759600001</v>
+        <v>-45.76438020000001</v>
       </c>
       <c r="Q51">
-        <v>20.60549240399999</v>
+        <v>19.33561979999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1951324212626342</v>
+        <v>0.1981190696878869</v>
       </c>
       <c r="T51">
-        <v>2.310125063531862</v>
+        <v>2.356327564802499</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06553328917349302</v>
+        <v>0.06422262339002315</v>
       </c>
       <c r="W51">
-        <v>0.2203472504128904</v>
+        <v>0.2206563054046325</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2849273442325784</v>
+        <v>0.2792287973479267</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5652,22 +5652,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2093876875462597</v>
+        <v>0.2112876875462597</v>
       </c>
       <c r="C52">
-        <v>128.4195638679618</v>
+        <v>118.5722084115535</v>
       </c>
       <c r="D52">
-        <v>311.6195638679619</v>
+        <v>308.7662084115536</v>
       </c>
       <c r="E52">
-        <v>313.5000000000001</v>
+        <v>320.4940000000001</v>
       </c>
       <c r="F52">
-        <v>349.7</v>
+        <v>356.6940000000001</v>
       </c>
       <c r="G52">
         <v>166.5</v>
@@ -5688,37 +5688,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M52">
-        <v>82.45926000000001</v>
+        <v>84.10844520000002</v>
       </c>
       <c r="N52">
-        <v>-59.43426000000001</v>
+        <v>-61.08344520000001</v>
       </c>
       <c r="O52">
-        <v>-13.6698798</v>
+        <v>-14.049192396</v>
       </c>
       <c r="P52">
-        <v>-45.76438020000001</v>
+        <v>-47.03425280400001</v>
       </c>
       <c r="Q52">
-        <v>19.33561979999999</v>
+        <v>18.06574719599998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1981190696878869</v>
+        <v>0.2012276221304968</v>
       </c>
       <c r="T52">
-        <v>2.356327564802499</v>
+        <v>2.404415882451529</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06422262339002315</v>
+        <v>0.06296335626472857</v>
       </c>
       <c r="W52">
-        <v>0.2206563054046325</v>
+        <v>0.220953240592777</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2792287973479267</v>
+        <v>0.2737537228901242</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5734,22 +5734,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2112876875462597</v>
+        <v>0.2131876875462597</v>
       </c>
       <c r="C53">
-        <v>118.5722084115535</v>
+        <v>108.7766325320838</v>
       </c>
       <c r="D53">
-        <v>308.7662084115536</v>
+        <v>305.9646325320838</v>
       </c>
       <c r="E53">
-        <v>320.4940000000001</v>
+        <v>327.4880000000001</v>
       </c>
       <c r="F53">
-        <v>356.6940000000001</v>
+        <v>363.688</v>
       </c>
       <c r="G53">
         <v>166.5</v>
@@ -5770,37 +5770,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M53">
-        <v>84.10844520000002</v>
+        <v>85.75763040000001</v>
       </c>
       <c r="N53">
-        <v>-61.08344520000001</v>
+        <v>-62.73263040000001</v>
       </c>
       <c r="O53">
-        <v>-14.049192396</v>
+        <v>-14.428504992</v>
       </c>
       <c r="P53">
-        <v>-47.03425280400001</v>
+        <v>-48.304125408</v>
       </c>
       <c r="Q53">
-        <v>18.06574719599998</v>
+        <v>16.79587459199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2012276221304968</v>
+        <v>0.2044656975915489</v>
       </c>
       <c r="T53">
-        <v>2.404415882451529</v>
+        <v>2.454507880002603</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06296335626472857</v>
+        <v>0.06175252249040688</v>
       </c>
       <c r="W53">
-        <v>0.220953240592777</v>
+        <v>0.2212387551967621</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2737537228901242</v>
+        <v>0.2684892282191603</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5816,22 +5816,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2131876875462597</v>
+        <v>0.2150876875462597</v>
       </c>
       <c r="C54">
-        <v>108.7766325320838</v>
+        <v>99.03143944444395</v>
       </c>
       <c r="D54">
-        <v>305.9646325320838</v>
+        <v>303.213439444444</v>
       </c>
       <c r="E54">
-        <v>327.4880000000001</v>
+        <v>334.4820000000001</v>
       </c>
       <c r="F54">
-        <v>363.688</v>
+        <v>370.6820000000001</v>
       </c>
       <c r="G54">
         <v>166.5</v>
@@ -5852,37 +5852,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M54">
-        <v>85.75763040000001</v>
+        <v>87.40681560000002</v>
       </c>
       <c r="N54">
-        <v>-62.73263040000001</v>
+        <v>-64.38181560000001</v>
       </c>
       <c r="O54">
-        <v>-14.428504992</v>
+        <v>-14.807817588</v>
       </c>
       <c r="P54">
-        <v>-48.304125408</v>
+        <v>-49.573998012</v>
       </c>
       <c r="Q54">
-        <v>16.79587459199999</v>
+        <v>15.52600198799999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2044656975915489</v>
+        <v>0.207841563497752</v>
       </c>
       <c r="T54">
-        <v>2.454507880002603</v>
+        <v>2.506731451917552</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06175252249040688</v>
+        <v>0.06058738055662561</v>
       </c>
       <c r="W54">
-        <v>0.2212387551967621</v>
+        <v>0.2215134956647477</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2684892282191603</v>
+        <v>0.2634233937244592</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5898,22 +5898,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2150876875462597</v>
+        <v>0.2169876875462597</v>
       </c>
       <c r="C55">
-        <v>99.03143944444395</v>
+        <v>89.3352821546307</v>
       </c>
       <c r="D55">
-        <v>303.213439444444</v>
+        <v>300.5112821546308</v>
       </c>
       <c r="E55">
-        <v>334.4820000000001</v>
+        <v>341.4760000000001</v>
       </c>
       <c r="F55">
-        <v>370.6820000000001</v>
+        <v>377.6760000000001</v>
       </c>
       <c r="G55">
         <v>166.5</v>
@@ -5934,37 +5934,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M55">
-        <v>87.40681560000002</v>
+        <v>89.05600080000002</v>
       </c>
       <c r="N55">
-        <v>-64.38181560000001</v>
+        <v>-66.03100080000002</v>
       </c>
       <c r="O55">
-        <v>-14.807817588</v>
+        <v>-15.187130184</v>
       </c>
       <c r="P55">
-        <v>-49.573998012</v>
+        <v>-50.84387061600001</v>
       </c>
       <c r="Q55">
-        <v>15.52600198799999</v>
+        <v>14.25612938399998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.207841563497752</v>
+        <v>0.2113642061824857</v>
       </c>
       <c r="T55">
-        <v>2.506731451917552</v>
+        <v>2.561225613915759</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06058738055662561</v>
+        <v>0.05946539202779921</v>
       </c>
       <c r="W55">
-        <v>0.2215134956647477</v>
+        <v>0.2217780605598449</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2634233937244592</v>
+        <v>0.2585451827295617</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5980,22 +5980,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2169876875462597</v>
+        <v>0.2188876875462598</v>
       </c>
       <c r="C56">
-        <v>89.3352821546307</v>
+        <v>79.68686126071776</v>
       </c>
       <c r="D56">
-        <v>300.5112821546308</v>
+        <v>297.8568612607178</v>
       </c>
       <c r="E56">
-        <v>341.4760000000001</v>
+        <v>348.4700000000001</v>
       </c>
       <c r="F56">
-        <v>377.6760000000001</v>
+        <v>384.6700000000001</v>
       </c>
       <c r="G56">
         <v>166.5</v>
@@ -6016,37 +6016,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M56">
-        <v>89.05600080000002</v>
+        <v>90.70518600000003</v>
       </c>
       <c r="N56">
-        <v>-66.03100080000002</v>
+        <v>-67.68018600000002</v>
       </c>
       <c r="O56">
-        <v>-15.187130184</v>
+        <v>-15.56644278000001</v>
       </c>
       <c r="P56">
-        <v>-50.84387061600001</v>
+        <v>-52.11374322000002</v>
       </c>
       <c r="Q56">
-        <v>14.25612938399998</v>
+        <v>12.98625677999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2113642061824857</v>
+        <v>0.2150434107643188</v>
       </c>
       <c r="T56">
-        <v>2.561225613915759</v>
+        <v>2.618141738669443</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05946539202779921</v>
+        <v>0.05838420308183922</v>
       </c>
       <c r="W56">
-        <v>0.2217780605598449</v>
+        <v>0.2220330049133023</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2585451827295617</v>
+        <v>0.2538443612253879</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6062,22 +6062,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2188876875462598</v>
+        <v>0.2207876875462597</v>
       </c>
       <c r="C57">
-        <v>79.68686126071776</v>
+        <v>70.08492286935171</v>
       </c>
       <c r="D57">
-        <v>297.8568612607178</v>
+        <v>295.2489228693518</v>
       </c>
       <c r="E57">
-        <v>348.4700000000001</v>
+        <v>355.4640000000001</v>
       </c>
       <c r="F57">
-        <v>384.6700000000001</v>
+        <v>391.6640000000001</v>
       </c>
       <c r="G57">
         <v>166.5</v>
@@ -6098,37 +6098,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M57">
-        <v>90.70518600000003</v>
+        <v>92.35437120000003</v>
       </c>
       <c r="N57">
-        <v>-67.68018600000002</v>
+        <v>-69.32937120000003</v>
       </c>
       <c r="O57">
-        <v>-15.56644278000001</v>
+        <v>-15.94575537600001</v>
       </c>
       <c r="P57">
-        <v>-52.11374322000002</v>
+        <v>-53.38361582400002</v>
       </c>
       <c r="Q57">
-        <v>12.98625677999998</v>
+        <v>11.71638417599998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2150434107643188</v>
+        <v>0.2188898519180533</v>
       </c>
       <c r="T57">
-        <v>2.618141738669443</v>
+        <v>2.67764496000284</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05838420308183922</v>
+        <v>0.05734162802680638</v>
       </c>
       <c r="W57">
-        <v>0.2220330049133023</v>
+        <v>0.222278844111279</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2538443612253879</v>
+        <v>0.249311426203506</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6144,22 +6144,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2207876875462597</v>
+        <v>0.2226876875462597</v>
       </c>
       <c r="C58">
-        <v>70.08492286935171</v>
+        <v>60.52825662075276</v>
       </c>
       <c r="D58">
-        <v>295.2489228693518</v>
+        <v>292.6862566207528</v>
       </c>
       <c r="E58">
-        <v>355.4640000000001</v>
+        <v>362.4580000000001</v>
       </c>
       <c r="F58">
-        <v>391.6640000000001</v>
+        <v>398.6580000000001</v>
       </c>
       <c r="G58">
         <v>166.5</v>
@@ -6180,37 +6180,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M58">
-        <v>92.35437120000003</v>
+        <v>94.00355640000002</v>
       </c>
       <c r="N58">
-        <v>-69.32937120000003</v>
+        <v>-70.97855640000002</v>
       </c>
       <c r="O58">
-        <v>-15.94575537600001</v>
+        <v>-16.325067972</v>
       </c>
       <c r="P58">
-        <v>-53.38361582400002</v>
+        <v>-54.65348842800002</v>
       </c>
       <c r="Q58">
-        <v>11.71638417599998</v>
+        <v>10.44651157199998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2188898519180533</v>
+        <v>0.2229151973114964</v>
       </c>
       <c r="T58">
-        <v>2.67764496000284</v>
+        <v>2.739915773026162</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05734162802680638</v>
+        <v>0.05633563455265189</v>
       </c>
       <c r="W58">
-        <v>0.222278844111279</v>
+        <v>0.2225160573724847</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.249311426203506</v>
+        <v>0.2449375415332691</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6226,22 +6226,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2226876875462597</v>
+        <v>0.2245876875462597</v>
       </c>
       <c r="C59">
-        <v>60.52825662075276</v>
+        <v>51.01569381568424</v>
       </c>
       <c r="D59">
-        <v>292.6862566207528</v>
+        <v>290.1676938156843</v>
       </c>
       <c r="E59">
-        <v>362.4580000000001</v>
+        <v>369.4520000000001</v>
       </c>
       <c r="F59">
-        <v>398.6580000000001</v>
+        <v>405.6520000000001</v>
       </c>
       <c r="G59">
         <v>166.5</v>
@@ -6262,37 +6262,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M59">
-        <v>94.00355640000002</v>
+        <v>95.65274160000003</v>
       </c>
       <c r="N59">
-        <v>-70.97855640000002</v>
+        <v>-72.62774160000002</v>
       </c>
       <c r="O59">
-        <v>-16.325067972</v>
+        <v>-16.704380568</v>
       </c>
       <c r="P59">
-        <v>-54.65348842800002</v>
+        <v>-55.92336103200002</v>
       </c>
       <c r="Q59">
-        <v>10.44651157199998</v>
+        <v>9.176638967999978</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2229151973114964</v>
+        <v>0.227132225818913</v>
       </c>
       <c r="T59">
-        <v>2.739915773026162</v>
+        <v>2.805151862860118</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05633563455265189</v>
+        <v>0.05536433050864064</v>
       </c>
       <c r="W59">
-        <v>0.2225160573724847</v>
+        <v>0.2227450908660625</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2449375415332691</v>
+        <v>0.2407144804723507</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2245876875462597</v>
+        <v>0.2264876875462598</v>
       </c>
       <c r="C60">
-        <v>51.0156938156843</v>
+        <v>41.54610563830261</v>
       </c>
       <c r="D60">
-        <v>290.1676938156843</v>
+        <v>287.6921056383026</v>
       </c>
       <c r="E60">
-        <v>369.4520000000001</v>
+        <v>376.446</v>
       </c>
       <c r="F60">
-        <v>405.652</v>
+        <v>412.646</v>
       </c>
       <c r="G60">
         <v>166.5</v>
@@ -6344,37 +6344,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M60">
-        <v>95.65274160000001</v>
+        <v>97.3019268</v>
       </c>
       <c r="N60">
-        <v>-72.62774160000001</v>
+        <v>-74.2769268</v>
       </c>
       <c r="O60">
-        <v>-16.704380568</v>
+        <v>-17.083693164</v>
       </c>
       <c r="P60">
-        <v>-55.923361032</v>
+        <v>-57.193233636</v>
       </c>
       <c r="Q60">
-        <v>9.176638967999992</v>
+        <v>7.906766363999992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.227132225818913</v>
+        <v>0.2315549630340084</v>
       </c>
       <c r="T60">
-        <v>2.805151862860118</v>
+        <v>2.873570200978657</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05536433050864065</v>
+        <v>0.05442595202544336</v>
       </c>
       <c r="W60">
-        <v>0.2227450908660625</v>
+        <v>0.2229663605124005</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2407144804723507</v>
+        <v>0.2366345740236667</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6390,22 +6390,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2264876875462598</v>
+        <v>0.2283876875462597</v>
       </c>
       <c r="C61">
-        <v>41.54610563830261</v>
+        <v>32.11840146920747</v>
       </c>
       <c r="D61">
-        <v>287.6921056383026</v>
+        <v>285.2584014692075</v>
       </c>
       <c r="E61">
-        <v>376.446</v>
+        <v>383.4400000000001</v>
       </c>
       <c r="F61">
-        <v>412.646</v>
+        <v>419.64</v>
       </c>
       <c r="G61">
         <v>166.5</v>
@@ -6426,37 +6426,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M61">
-        <v>97.3019268</v>
+        <v>98.95111200000001</v>
       </c>
       <c r="N61">
-        <v>-74.2769268</v>
+        <v>-75.926112</v>
       </c>
       <c r="O61">
-        <v>-17.083693164</v>
+        <v>-17.46300576</v>
       </c>
       <c r="P61">
-        <v>-57.193233636</v>
+        <v>-58.46310624</v>
       </c>
       <c r="Q61">
-        <v>7.906766363999992</v>
+        <v>6.636893759999992</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2315549630340084</v>
+        <v>0.2361988371098586</v>
       </c>
       <c r="T61">
-        <v>2.873570200978657</v>
+        <v>2.945409456003123</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05442595202544336</v>
+        <v>0.05351885282501929</v>
       </c>
       <c r="W61">
-        <v>0.2229663605124005</v>
+        <v>0.2231802545038604</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2366345740236667</v>
+        <v>0.2326906644566057</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6472,22 +6472,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2283876875462597</v>
+        <v>0.2302876875462598</v>
       </c>
       <c r="C62">
-        <v>32.11840146920747</v>
+        <v>22.73152728339835</v>
       </c>
       <c r="D62">
-        <v>285.2584014692075</v>
+        <v>282.8655272833984</v>
       </c>
       <c r="E62">
-        <v>383.4400000000001</v>
+        <v>390.4340000000001</v>
       </c>
       <c r="F62">
-        <v>419.64</v>
+        <v>426.6340000000001</v>
       </c>
       <c r="G62">
         <v>166.5</v>
@@ -6508,37 +6508,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M62">
-        <v>98.95111200000001</v>
+        <v>100.6002972</v>
       </c>
       <c r="N62">
-        <v>-75.926112</v>
+        <v>-77.57529720000001</v>
       </c>
       <c r="O62">
-        <v>-17.46300576</v>
+        <v>-17.842318356</v>
       </c>
       <c r="P62">
-        <v>-58.46310624</v>
+        <v>-59.732978844</v>
       </c>
       <c r="Q62">
-        <v>6.636893759999992</v>
+        <v>5.367021155999993</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2361988371098586</v>
+        <v>0.241080858574214</v>
       </c>
       <c r="T62">
-        <v>2.945409456003123</v>
+        <v>3.020932775387819</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05351885282501929</v>
+        <v>0.05264149458198619</v>
       </c>
       <c r="W62">
-        <v>0.2231802545038604</v>
+        <v>0.2233871355775677</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2326906644566057</v>
+        <v>0.2288760633999399</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6554,22 +6554,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2302876875462598</v>
+        <v>0.2321876875462597</v>
       </c>
       <c r="C63">
-        <v>22.73152728339835</v>
+        <v>13.38446412819292</v>
       </c>
       <c r="D63">
-        <v>282.8655272833984</v>
+        <v>280.512464128193</v>
       </c>
       <c r="E63">
-        <v>390.4340000000001</v>
+        <v>397.4280000000001</v>
       </c>
       <c r="F63">
-        <v>426.6340000000001</v>
+        <v>433.628</v>
       </c>
       <c r="G63">
         <v>166.5</v>
@@ -6590,37 +6590,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M63">
-        <v>100.6002972</v>
+        <v>102.2494824</v>
       </c>
       <c r="N63">
-        <v>-77.57529720000001</v>
+        <v>-79.22448240000001</v>
       </c>
       <c r="O63">
-        <v>-17.842318356</v>
+        <v>-18.22163095200001</v>
       </c>
       <c r="P63">
-        <v>-59.732978844</v>
+        <v>-61.00285144800001</v>
       </c>
       <c r="Q63">
-        <v>5.367021155999993</v>
+        <v>4.097148551999986</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.241080858574214</v>
+        <v>0.2462198285366933</v>
       </c>
       <c r="T63">
-        <v>3.020932775387819</v>
+        <v>3.100431006319077</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05264149458198619</v>
+        <v>0.0517924382177606</v>
       </c>
       <c r="W63">
-        <v>0.2233871355775677</v>
+        <v>0.2235873430682521</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2288760633999399</v>
+        <v>0.2251845139902635</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6636,22 +6636,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2321876875462597</v>
+        <v>0.2340876875462597</v>
       </c>
       <c r="C64">
-        <v>13.38446412819292</v>
+        <v>4.076226676486385</v>
       </c>
       <c r="D64">
-        <v>280.512464128193</v>
+        <v>278.1982266764865</v>
       </c>
       <c r="E64">
-        <v>397.4280000000001</v>
+        <v>404.4220000000001</v>
       </c>
       <c r="F64">
-        <v>433.628</v>
+        <v>440.6220000000001</v>
       </c>
       <c r="G64">
         <v>166.5</v>
@@ -6672,37 +6672,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M64">
-        <v>102.2494824</v>
+        <v>103.8986676</v>
       </c>
       <c r="N64">
-        <v>-79.22448240000001</v>
+        <v>-80.87366760000002</v>
       </c>
       <c r="O64">
-        <v>-18.22163095200001</v>
+        <v>-18.600943548</v>
       </c>
       <c r="P64">
-        <v>-61.00285144800001</v>
+        <v>-62.27272405200002</v>
       </c>
       <c r="Q64">
-        <v>4.097148551999986</v>
+        <v>2.827275947999979</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2462198285366933</v>
+        <v>0.2516365806593066</v>
       </c>
       <c r="T64">
-        <v>3.100431006319077</v>
+        <v>3.184226438922295</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0517924382177606</v>
+        <v>0.0509703360238279</v>
       </c>
       <c r="W64">
-        <v>0.2235873430682521</v>
+        <v>0.2237811947655814</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2251845139902635</v>
+        <v>0.2216101566253387</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6718,22 +6718,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2340876875462597</v>
+        <v>0.2359876875462597</v>
       </c>
       <c r="C65">
-        <v>4.076226676486385</v>
+        <v>-5.194138148958416</v>
       </c>
       <c r="D65">
-        <v>278.1982266764865</v>
+        <v>275.9218618510416</v>
       </c>
       <c r="E65">
-        <v>404.4220000000001</v>
+        <v>411.4160000000001</v>
       </c>
       <c r="F65">
-        <v>440.6220000000001</v>
+        <v>447.616</v>
       </c>
       <c r="G65">
         <v>166.5</v>
@@ -6754,37 +6754,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M65">
-        <v>103.8986676</v>
+        <v>105.5478528</v>
       </c>
       <c r="N65">
-        <v>-80.87366760000002</v>
+        <v>-82.52285280000001</v>
       </c>
       <c r="O65">
-        <v>-18.600943548</v>
+        <v>-18.980256144</v>
       </c>
       <c r="P65">
-        <v>-62.27272405200002</v>
+        <v>-63.54259665600001</v>
       </c>
       <c r="Q65">
-        <v>2.827275947999979</v>
+        <v>1.557403343999987</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2516365806593066</v>
+        <v>0.2573542634553984</v>
       </c>
       <c r="T65">
-        <v>3.184226438922295</v>
+        <v>3.272677173336803</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0509703360238279</v>
+        <v>0.05017392452345559</v>
       </c>
       <c r="W65">
-        <v>0.2237811947655814</v>
+        <v>0.2239689885973692</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2216101566253387</v>
+        <v>0.2181474979280678</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6800,22 +6800,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2359876875462597</v>
+        <v>0.2378876875462597</v>
       </c>
       <c r="C66">
-        <v>-5.194138148958416</v>
+        <v>-14.42755248423038</v>
       </c>
       <c r="D66">
-        <v>275.9218618510416</v>
+        <v>273.6824475157697</v>
       </c>
       <c r="E66">
-        <v>411.4160000000001</v>
+        <v>418.4100000000001</v>
       </c>
       <c r="F66">
-        <v>447.616</v>
+        <v>454.6100000000001</v>
       </c>
       <c r="G66">
         <v>166.5</v>
@@ -6836,37 +6836,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M66">
-        <v>105.5478528</v>
+        <v>107.197038</v>
       </c>
       <c r="N66">
-        <v>-82.52285280000001</v>
+        <v>-84.17203800000001</v>
       </c>
       <c r="O66">
-        <v>-18.980256144</v>
+        <v>-19.35956874</v>
       </c>
       <c r="P66">
-        <v>-63.54259665600001</v>
+        <v>-64.81246926000001</v>
       </c>
       <c r="Q66">
-        <v>1.557403343999987</v>
+        <v>0.2875307399999798</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2573542634553984</v>
+        <v>0.2633986709826956</v>
       </c>
       <c r="T66">
-        <v>3.272677173336803</v>
+        <v>3.366182235432142</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05017392452345559</v>
+        <v>0.0494020179923255</v>
       </c>
       <c r="W66">
-        <v>0.2239689885973692</v>
+        <v>0.2241510041574097</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2181474979280678</v>
+        <v>0.2147913825753283</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6882,22 +6882,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2378876875462597</v>
+        <v>0.2397876875462597</v>
       </c>
       <c r="C67">
-        <v>-14.42755248423038</v>
+        <v>-23.62490876977108</v>
       </c>
       <c r="D67">
-        <v>273.6824475157697</v>
+        <v>271.479091230229</v>
       </c>
       <c r="E67">
-        <v>418.4100000000001</v>
+        <v>425.4040000000001</v>
       </c>
       <c r="F67">
-        <v>454.6100000000001</v>
+        <v>461.6040000000001</v>
       </c>
       <c r="G67">
         <v>166.5</v>
@@ -6918,37 +6918,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M67">
-        <v>107.197038</v>
+        <v>108.8462232</v>
       </c>
       <c r="N67">
-        <v>-84.17203800000001</v>
+        <v>-85.82122320000002</v>
       </c>
       <c r="O67">
-        <v>-19.35956874</v>
+        <v>-19.73888133600001</v>
       </c>
       <c r="P67">
-        <v>-64.81246926000001</v>
+        <v>-66.08234186400001</v>
       </c>
       <c r="Q67">
-        <v>0.2875307399999798</v>
+        <v>-0.9823418640000199</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2633986709826956</v>
+        <v>0.2697986318939514</v>
       </c>
       <c r="T67">
-        <v>3.366182235432142</v>
+        <v>3.465187595297793</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0494020179923255</v>
+        <v>0.04865350256819935</v>
       </c>
       <c r="W67">
-        <v>0.2241510041574097</v>
+        <v>0.2243275040944186</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2147913825753283</v>
+        <v>0.2115369676878233</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6964,22 +6964,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2397876875462597</v>
+        <v>0.2416876875462597</v>
       </c>
       <c r="C68">
-        <v>-23.62490876977108</v>
+        <v>-32.78707093619329</v>
       </c>
       <c r="D68">
-        <v>271.479091230229</v>
+        <v>269.3109290638068</v>
       </c>
       <c r="E68">
-        <v>425.4040000000001</v>
+        <v>432.3980000000001</v>
       </c>
       <c r="F68">
-        <v>461.6040000000001</v>
+        <v>468.5980000000001</v>
       </c>
       <c r="G68">
         <v>166.5</v>
@@ -7000,37 +7000,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M68">
-        <v>108.8462232</v>
+        <v>110.4954084</v>
       </c>
       <c r="N68">
-        <v>-85.82122320000002</v>
+        <v>-87.47040840000001</v>
       </c>
       <c r="O68">
-        <v>-19.73888133600001</v>
+        <v>-20.118193932</v>
       </c>
       <c r="P68">
-        <v>-66.08234186400001</v>
+        <v>-67.352214468</v>
       </c>
       <c r="Q68">
-        <v>-0.9823418640000199</v>
+        <v>-2.252214468000005</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2697986318939514</v>
+        <v>0.2765864692240711</v>
       </c>
       <c r="T68">
-        <v>3.465187595297793</v>
+        <v>3.570193280003787</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04865350256819935</v>
+        <v>0.04792733088807698</v>
       </c>
       <c r="W68">
-        <v>0.2243275040944186</v>
+        <v>0.2244987353765915</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2115369676878233</v>
+        <v>0.2083796995133782</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7046,22 +7046,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2416876875462597</v>
+        <v>0.2435876875462597</v>
       </c>
       <c r="C69">
-        <v>-32.78707093619329</v>
+        <v>-41.91487553372673</v>
       </c>
       <c r="D69">
-        <v>269.3109290638068</v>
+        <v>267.1771244662734</v>
       </c>
       <c r="E69">
-        <v>432.3980000000001</v>
+        <v>439.3920000000001</v>
       </c>
       <c r="F69">
-        <v>468.5980000000001</v>
+        <v>475.5920000000001</v>
       </c>
       <c r="G69">
         <v>166.5</v>
@@ -7082,37 +7082,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M69">
-        <v>110.4954084</v>
+        <v>112.1445936</v>
       </c>
       <c r="N69">
-        <v>-87.47040840000001</v>
+        <v>-89.11959360000002</v>
       </c>
       <c r="O69">
-        <v>-20.118193932</v>
+        <v>-20.49750652800001</v>
       </c>
       <c r="P69">
-        <v>-67.352214468</v>
+        <v>-68.62208707200001</v>
       </c>
       <c r="Q69">
-        <v>-2.252214468000005</v>
+        <v>-3.522087072000019</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2765864692240711</v>
+        <v>0.2837985463873233</v>
       </c>
       <c r="T69">
-        <v>3.570193280003787</v>
+        <v>3.681761820003905</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04792733088807698</v>
+        <v>0.04722251719854643</v>
       </c>
       <c r="W69">
-        <v>0.2244987353765915</v>
+        <v>0.2246649304445828</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2083796995133782</v>
+        <v>0.2053152921675931</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7128,22 +7128,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2435876875462597</v>
+        <v>0.2454876875462597</v>
       </c>
       <c r="C70">
-        <v>-41.91487553372673</v>
+        <v>-51.00913280839228</v>
       </c>
       <c r="D70">
-        <v>267.1771244662734</v>
+        <v>265.0768671916078</v>
       </c>
       <c r="E70">
-        <v>439.3920000000001</v>
+        <v>446.3860000000001</v>
       </c>
       <c r="F70">
-        <v>475.5920000000001</v>
+        <v>482.5860000000001</v>
       </c>
       <c r="G70">
         <v>166.5</v>
@@ -7164,37 +7164,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M70">
-        <v>112.1445936</v>
+        <v>113.7937788</v>
       </c>
       <c r="N70">
-        <v>-89.11959360000002</v>
+        <v>-90.76877880000004</v>
       </c>
       <c r="O70">
-        <v>-20.49750652800001</v>
+        <v>-20.87681912400001</v>
       </c>
       <c r="P70">
-        <v>-68.62208707200001</v>
+        <v>-69.89195967600003</v>
       </c>
       <c r="Q70">
-        <v>-3.522087072000019</v>
+        <v>-4.791959676000033</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2837985463873233</v>
+        <v>0.2914759188514305</v>
       </c>
       <c r="T70">
-        <v>3.681761820003905</v>
+        <v>3.800528330326612</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04722251719854643</v>
+        <v>0.04653813289132112</v>
       </c>
       <c r="W70">
-        <v>0.2246649304445828</v>
+        <v>0.2248263082642265</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2053152921675931</v>
+        <v>0.2023397082231353</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7210,22 +7210,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2454876875462597</v>
+        <v>0.2473876875462597</v>
       </c>
       <c r="C71">
-        <v>-51.00913280839228</v>
+        <v>-60.07062772781461</v>
       </c>
       <c r="D71">
-        <v>265.0768671916078</v>
+        <v>263.0093722721855</v>
       </c>
       <c r="E71">
-        <v>446.3860000000001</v>
+        <v>453.3800000000001</v>
       </c>
       <c r="F71">
-        <v>482.5860000000001</v>
+        <v>489.5800000000001</v>
       </c>
       <c r="G71">
         <v>166.5</v>
@@ -7246,37 +7246,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M71">
-        <v>113.7937788</v>
+        <v>115.442964</v>
       </c>
       <c r="N71">
-        <v>-90.76877880000004</v>
+        <v>-92.41796400000003</v>
       </c>
       <c r="O71">
-        <v>-20.87681912400001</v>
+        <v>-21.25613172000001</v>
       </c>
       <c r="P71">
-        <v>-69.89195967600003</v>
+        <v>-71.16183228000003</v>
       </c>
       <c r="Q71">
-        <v>-4.791959676000033</v>
+        <v>-6.061832280000033</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2914759188514305</v>
+        <v>0.2996651161464782</v>
       </c>
       <c r="T71">
-        <v>3.800528330326612</v>
+        <v>3.927212608004166</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04653813289132112</v>
+        <v>0.04587330242144511</v>
       </c>
       <c r="W71">
-        <v>0.2248263082642265</v>
+        <v>0.2249830752890233</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2023397082231353</v>
+        <v>0.1994491409628047</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7292,22 +7292,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2473876875462597</v>
+        <v>0.2492876875462597</v>
       </c>
       <c r="C72">
-        <v>-60.07062772781461</v>
+        <v>-69.10012095940004</v>
       </c>
       <c r="D72">
-        <v>263.0093722721855</v>
+        <v>260.9738790406001</v>
       </c>
       <c r="E72">
-        <v>453.3800000000001</v>
+        <v>460.3740000000001</v>
       </c>
       <c r="F72">
-        <v>489.5800000000001</v>
+        <v>496.5740000000001</v>
       </c>
       <c r="G72">
         <v>166.5</v>
@@ -7328,37 +7328,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M72">
-        <v>115.442964</v>
+        <v>117.0921492</v>
       </c>
       <c r="N72">
-        <v>-92.41796400000003</v>
+        <v>-94.06714920000003</v>
       </c>
       <c r="O72">
-        <v>-21.25613172000001</v>
+        <v>-21.63544431600001</v>
       </c>
       <c r="P72">
-        <v>-71.16183228000003</v>
+        <v>-72.43170488400003</v>
       </c>
       <c r="Q72">
-        <v>-6.061832280000033</v>
+        <v>-7.331704884000033</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2996651161464782</v>
+        <v>0.3084190856687706</v>
       </c>
       <c r="T72">
-        <v>3.927212608004166</v>
+        <v>4.062633732418103</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04587330242144511</v>
+        <v>0.04522719957043884</v>
       </c>
       <c r="W72">
-        <v>0.2249830752890233</v>
+        <v>0.2251354263412905</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1994491409628047</v>
+        <v>0.1966399981323428</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7374,22 +7374,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2492876875462597</v>
+        <v>0.2511876875462598</v>
       </c>
       <c r="C73">
-        <v>-69.10012095939987</v>
+        <v>-78.09834980344135</v>
       </c>
       <c r="D73">
-        <v>260.9738790406001</v>
+        <v>258.9696501965587</v>
       </c>
       <c r="E73">
-        <v>460.374</v>
+        <v>467.3680000000001</v>
       </c>
       <c r="F73">
-        <v>496.574</v>
+        <v>503.568</v>
       </c>
       <c r="G73">
         <v>166.5</v>
@@ -7410,37 +7410,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M73">
-        <v>117.0921492</v>
+        <v>118.7413344</v>
       </c>
       <c r="N73">
-        <v>-94.0671492</v>
+        <v>-95.71633440000001</v>
       </c>
       <c r="O73">
-        <v>-21.635444316</v>
+        <v>-22.014756912</v>
       </c>
       <c r="P73">
-        <v>-72.431704884</v>
+        <v>-73.701577488</v>
       </c>
       <c r="Q73">
-        <v>-7.331704884000004</v>
+        <v>-8.601577488000004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3084190856687705</v>
+        <v>0.3177983387283694</v>
       </c>
       <c r="T73">
-        <v>4.062633732418101</v>
+        <v>4.207727794290176</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04522719957043884</v>
+        <v>0.04459904402084941</v>
       </c>
       <c r="W73">
-        <v>0.2251354263412905</v>
+        <v>0.2252835454198837</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1966399981323428</v>
+        <v>0.1939088870471714</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7456,22 +7456,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2511876875462598</v>
+        <v>0.2530876875462597</v>
       </c>
       <c r="C74">
-        <v>-78.09834980344135</v>
+        <v>-87.06602908355438</v>
       </c>
       <c r="D74">
-        <v>258.9696501965587</v>
+        <v>256.9959709164457</v>
       </c>
       <c r="E74">
-        <v>467.3680000000001</v>
+        <v>474.3620000000001</v>
       </c>
       <c r="F74">
-        <v>503.568</v>
+        <v>510.5620000000001</v>
       </c>
       <c r="G74">
         <v>166.5</v>
@@ -7492,37 +7492,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M74">
-        <v>118.7413344</v>
+        <v>120.3905196</v>
       </c>
       <c r="N74">
-        <v>-95.71633440000001</v>
+        <v>-97.36551960000001</v>
       </c>
       <c r="O74">
-        <v>-22.014756912</v>
+        <v>-22.394069508</v>
       </c>
       <c r="P74">
-        <v>-73.701577488</v>
+        <v>-74.97145009200001</v>
       </c>
       <c r="Q74">
-        <v>-8.601577488000004</v>
+        <v>-9.871450092000018</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3177983387283694</v>
+        <v>0.3278723512738646</v>
       </c>
       <c r="T74">
-        <v>4.207727794290176</v>
+        <v>4.363569564449072</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04459904402084941</v>
+        <v>0.04398809821234463</v>
       </c>
       <c r="W74">
-        <v>0.2252835454198837</v>
+        <v>0.2254276064415291</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1939088870471714</v>
+        <v>0.1912526009232375</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7538,22 +7538,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2530876875462597</v>
+        <v>0.2549876875462597</v>
       </c>
       <c r="C75">
-        <v>-87.06602908355438</v>
+        <v>-96.00385199670404</v>
       </c>
       <c r="D75">
-        <v>256.9959709164457</v>
+        <v>255.052148003296</v>
       </c>
       <c r="E75">
-        <v>474.3620000000001</v>
+        <v>481.3560000000001</v>
       </c>
       <c r="F75">
-        <v>510.5620000000001</v>
+        <v>517.556</v>
       </c>
       <c r="G75">
         <v>166.5</v>
@@ -7574,37 +7574,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M75">
-        <v>120.3905196</v>
+        <v>122.0397048</v>
       </c>
       <c r="N75">
-        <v>-97.36551960000001</v>
+        <v>-99.0147048</v>
       </c>
       <c r="O75">
-        <v>-22.394069508</v>
+        <v>-22.773382104</v>
       </c>
       <c r="P75">
-        <v>-74.97145009200001</v>
+        <v>-76.241322696</v>
       </c>
       <c r="Q75">
-        <v>-9.871450092000018</v>
+        <v>-11.141322696</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3278723512738646</v>
+        <v>0.3387212878613209</v>
       </c>
       <c r="T75">
-        <v>4.363569564449072</v>
+        <v>4.531399163081728</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04398809821234463</v>
+        <v>0.04339366445271835</v>
       </c>
       <c r="W75">
-        <v>0.2254276064415291</v>
+        <v>0.225567773922049</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1912526009232375</v>
+        <v>0.1886681063161667</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7620,22 +7620,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2549876875462597</v>
+        <v>0.2568876875462597</v>
       </c>
       <c r="C76">
-        <v>-96.00385199670404</v>
+        <v>-104.9124909249451</v>
       </c>
       <c r="D76">
-        <v>255.052148003296</v>
+        <v>253.1375090750549</v>
       </c>
       <c r="E76">
-        <v>481.3560000000001</v>
+        <v>488.3500000000001</v>
       </c>
       <c r="F76">
-        <v>517.556</v>
+        <v>524.5500000000001</v>
       </c>
       <c r="G76">
         <v>166.5</v>
@@ -7656,37 +7656,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M76">
-        <v>122.0397048</v>
+        <v>123.68889</v>
       </c>
       <c r="N76">
-        <v>-99.0147048</v>
+        <v>-100.66389</v>
       </c>
       <c r="O76">
-        <v>-22.773382104</v>
+        <v>-23.1526947</v>
       </c>
       <c r="P76">
-        <v>-76.241322696</v>
+        <v>-77.51119530000001</v>
       </c>
       <c r="Q76">
-        <v>-11.141322696</v>
+        <v>-12.41119530000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3387212878613209</v>
+        <v>0.3504381393757738</v>
       </c>
       <c r="T76">
-        <v>4.531399163081728</v>
+        <v>4.712655129604998</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04339366445271835</v>
+        <v>0.04281508226001544</v>
       </c>
       <c r="W76">
-        <v>0.225567773922049</v>
+        <v>0.2257042036030884</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1886681063161667</v>
+        <v>0.1861525315652846</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7702,22 +7702,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2568876875462597</v>
+        <v>0.2587876875462597</v>
       </c>
       <c r="C77">
-        <v>-104.9124909249451</v>
+        <v>-113.7925982108731</v>
       </c>
       <c r="D77">
-        <v>253.1375090750549</v>
+        <v>251.251401789127</v>
       </c>
       <c r="E77">
-        <v>488.3500000000001</v>
+        <v>495.3440000000001</v>
       </c>
       <c r="F77">
-        <v>524.5500000000001</v>
+        <v>531.5440000000001</v>
       </c>
       <c r="G77">
         <v>166.5</v>
@@ -7738,37 +7738,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M77">
-        <v>123.68889</v>
+        <v>125.3380752</v>
       </c>
       <c r="N77">
-        <v>-100.66389</v>
+        <v>-102.3130752</v>
       </c>
       <c r="O77">
-        <v>-23.1526947</v>
+        <v>-23.53200729600001</v>
       </c>
       <c r="P77">
-        <v>-77.51119530000001</v>
+        <v>-78.78106790400003</v>
       </c>
       <c r="Q77">
-        <v>-12.41119530000002</v>
+        <v>-13.68106790400003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3504381393757738</v>
+        <v>0.3631313951830977</v>
       </c>
       <c r="T77">
-        <v>4.712655129604998</v>
+        <v>4.909015760005206</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04281508226001544</v>
+        <v>0.04225172591448891</v>
       </c>
       <c r="W77">
-        <v>0.2257042036030884</v>
+        <v>0.2258370430293635</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1861525315652846</v>
+        <v>0.1837031561499518</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7784,22 +7784,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2587876875462597</v>
+        <v>0.2606876875462597</v>
       </c>
       <c r="C78">
-        <v>-113.7925982108731</v>
+        <v>-122.644806898665</v>
       </c>
       <c r="D78">
-        <v>251.251401789127</v>
+        <v>249.3931931013351</v>
       </c>
       <c r="E78">
-        <v>495.3440000000001</v>
+        <v>502.3380000000001</v>
       </c>
       <c r="F78">
-        <v>531.5440000000001</v>
+        <v>538.5380000000001</v>
       </c>
       <c r="G78">
         <v>166.5</v>
@@ -7820,37 +7820,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M78">
-        <v>125.3380752</v>
+        <v>126.9872604</v>
       </c>
       <c r="N78">
-        <v>-102.3130752</v>
+        <v>-103.9622604</v>
       </c>
       <c r="O78">
-        <v>-23.53200729600001</v>
+        <v>-23.91131989200001</v>
       </c>
       <c r="P78">
-        <v>-78.78106790400003</v>
+        <v>-80.05094050800002</v>
       </c>
       <c r="Q78">
-        <v>-13.68106790400003</v>
+        <v>-14.95094050800003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3631313951830977</v>
+        <v>0.3769284123649715</v>
       </c>
       <c r="T78">
-        <v>4.909015760005206</v>
+        <v>5.122451227831519</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04225172591448891</v>
+        <v>0.04170300220131373</v>
       </c>
       <c r="W78">
-        <v>0.2258370430293635</v>
+        <v>0.2259664320809302</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1837031561499518</v>
+        <v>0.181317400875277</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7866,22 +7866,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2606876875462597</v>
+        <v>0.2625876875462597</v>
       </c>
       <c r="C79">
-        <v>-122.644806898665</v>
+        <v>-131.4697314424776</v>
       </c>
       <c r="D79">
-        <v>249.3931931013351</v>
+        <v>247.5622685575224</v>
       </c>
       <c r="E79">
-        <v>502.3380000000001</v>
+        <v>509.3320000000001</v>
       </c>
       <c r="F79">
-        <v>538.5380000000001</v>
+        <v>545.532</v>
       </c>
       <c r="G79">
         <v>166.5</v>
@@ -7902,37 +7902,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M79">
-        <v>126.9872604</v>
+        <v>128.6364456</v>
       </c>
       <c r="N79">
-        <v>-103.9622604</v>
+        <v>-105.6114456</v>
       </c>
       <c r="O79">
-        <v>-23.91131989200001</v>
+        <v>-24.290632488</v>
       </c>
       <c r="P79">
-        <v>-80.05094050800002</v>
+        <v>-81.320813112</v>
       </c>
       <c r="Q79">
-        <v>-14.95094050800003</v>
+        <v>-16.220813112</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3769284123649715</v>
+        <v>0.3919797038361066</v>
       </c>
       <c r="T79">
-        <v>5.122451227831519</v>
+        <v>5.35528992000568</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04170300220131373</v>
+        <v>0.04116834832693792</v>
       </c>
       <c r="W79">
-        <v>0.2259664320809302</v>
+        <v>0.226092503464508</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.181317400875277</v>
+        <v>0.1789928188127736</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7948,22 +7948,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2625876875462597</v>
+        <v>0.2644876875462597</v>
       </c>
       <c r="C80">
-        <v>-131.4697314424776</v>
+        <v>-140.2679683838694</v>
       </c>
       <c r="D80">
-        <v>247.5622685575224</v>
+        <v>245.7580316161307</v>
       </c>
       <c r="E80">
-        <v>509.3320000000001</v>
+        <v>516.326</v>
       </c>
       <c r="F80">
-        <v>545.532</v>
+        <v>552.5260000000001</v>
       </c>
       <c r="G80">
         <v>166.5</v>
@@ -7984,37 +7984,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M80">
-        <v>128.6364456</v>
+        <v>130.2856308</v>
       </c>
       <c r="N80">
-        <v>-105.6114456</v>
+        <v>-107.2606308</v>
       </c>
       <c r="O80">
-        <v>-24.290632488</v>
+        <v>-24.66994508400001</v>
       </c>
       <c r="P80">
-        <v>-81.320813112</v>
+        <v>-82.59068571600002</v>
       </c>
       <c r="Q80">
-        <v>-16.220813112</v>
+        <v>-17.49068571600003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3919797038361066</v>
+        <v>0.4084644516378261</v>
       </c>
       <c r="T80">
-        <v>5.35528992000568</v>
+        <v>5.610303725720237</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04116834832693792</v>
+        <v>0.04064722999368554</v>
       </c>
       <c r="W80">
-        <v>0.226092503464508</v>
+        <v>0.226215383167489</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1789928188127736</v>
+        <v>0.1767270869290676</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8030,22 +8030,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2644876875462597</v>
+        <v>0.2663876875462597</v>
       </c>
       <c r="C81">
-        <v>-140.2679683838694</v>
+        <v>-149.0400969998134</v>
       </c>
       <c r="D81">
-        <v>245.7580316161307</v>
+        <v>243.9799030001867</v>
       </c>
       <c r="E81">
-        <v>516.326</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="F81">
-        <v>552.5260000000001</v>
+        <v>559.5200000000001</v>
       </c>
       <c r="G81">
         <v>166.5</v>
@@ -8066,37 +8066,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M81">
-        <v>130.2856308</v>
+        <v>131.934816</v>
       </c>
       <c r="N81">
-        <v>-107.2606308</v>
+        <v>-108.909816</v>
       </c>
       <c r="O81">
-        <v>-24.66994508400001</v>
+        <v>-25.04925768000001</v>
       </c>
       <c r="P81">
-        <v>-82.59068571600002</v>
+        <v>-83.86055832000002</v>
       </c>
       <c r="Q81">
-        <v>-17.49068571600003</v>
+        <v>-18.76055832000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4084644516378261</v>
+        <v>0.4265976742197173</v>
       </c>
       <c r="T81">
-        <v>5.610303725720237</v>
+        <v>5.890818912006248</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04064722999368554</v>
+        <v>0.04013913961876446</v>
       </c>
       <c r="W81">
-        <v>0.226215383167489</v>
+        <v>0.2263351908778954</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1767270869290676</v>
+        <v>0.1745179983424542</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8112,22 +8112,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2663876875462597</v>
+        <v>0.2682876875462598</v>
       </c>
       <c r="C82">
-        <v>-149.0400969998134</v>
+        <v>-157.7866799227815</v>
       </c>
       <c r="D82">
-        <v>243.9799030001867</v>
+        <v>242.2273200772186</v>
       </c>
       <c r="E82">
-        <v>523.3200000000001</v>
+        <v>530.3140000000001</v>
       </c>
       <c r="F82">
-        <v>559.5200000000001</v>
+        <v>566.5140000000001</v>
       </c>
       <c r="G82">
         <v>166.5</v>
@@ -8148,37 +8148,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M82">
-        <v>131.934816</v>
+        <v>133.5840012</v>
       </c>
       <c r="N82">
-        <v>-108.909816</v>
+        <v>-110.5590012</v>
       </c>
       <c r="O82">
-        <v>-25.04925768000001</v>
+        <v>-25.42857027600001</v>
       </c>
       <c r="P82">
-        <v>-83.86055832000002</v>
+        <v>-85.13043092400002</v>
       </c>
       <c r="Q82">
-        <v>-18.76055832000003</v>
+        <v>-20.03043092400003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4265976742197173</v>
+        <v>0.4466396570733867</v>
       </c>
       <c r="T82">
-        <v>5.890818912006248</v>
+        <v>6.200862012638156</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04013913961876446</v>
+        <v>0.03964359468519947</v>
       </c>
       <c r="W82">
-        <v>0.2263351908778954</v>
+        <v>0.22645204037323</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1745179983424542</v>
+        <v>0.1723634551530412</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8194,22 +8194,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2682876875462598</v>
+        <v>0.2701876875462597</v>
       </c>
       <c r="C83">
-        <v>-157.7866799227815</v>
+        <v>-166.5082637342944</v>
       </c>
       <c r="D83">
-        <v>242.2273200772186</v>
+        <v>240.4997362657057</v>
       </c>
       <c r="E83">
-        <v>530.3140000000001</v>
+        <v>537.3080000000001</v>
       </c>
       <c r="F83">
-        <v>566.5140000000001</v>
+        <v>573.5080000000002</v>
       </c>
       <c r="G83">
         <v>166.5</v>
@@ -8230,37 +8230,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M83">
-        <v>133.5840012</v>
+        <v>135.2331864000001</v>
       </c>
       <c r="N83">
-        <v>-110.5590012</v>
+        <v>-112.2081864</v>
       </c>
       <c r="O83">
-        <v>-25.42857027600001</v>
+        <v>-25.80788287200001</v>
       </c>
       <c r="P83">
-        <v>-85.13043092400002</v>
+        <v>-86.40030352800004</v>
       </c>
       <c r="Q83">
-        <v>-20.03043092400003</v>
+        <v>-21.30030352800004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4466396570733867</v>
+        <v>0.468908526910797</v>
       </c>
       <c r="T83">
-        <v>6.200862012638156</v>
+        <v>6.545354346673609</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03964359468519947</v>
+        <v>0.03916013621342875</v>
       </c>
       <c r="W83">
-        <v>0.22645204037323</v>
+        <v>0.2265660398808735</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1723634551530412</v>
+        <v>0.1702614617975162</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8276,22 +8276,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2701876875462597</v>
+        <v>0.2720876875462597</v>
       </c>
       <c r="C84">
-        <v>-166.5082637342944</v>
+        <v>-175.2053795332507</v>
       </c>
       <c r="D84">
-        <v>240.4997362657057</v>
+        <v>238.7966204667494</v>
       </c>
       <c r="E84">
-        <v>537.3080000000001</v>
+        <v>544.3020000000001</v>
       </c>
       <c r="F84">
-        <v>573.5080000000002</v>
+        <v>580.5020000000002</v>
       </c>
       <c r="G84">
         <v>166.5</v>
@@ -8312,37 +8312,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M84">
-        <v>135.2331864000001</v>
+        <v>136.8823716000001</v>
       </c>
       <c r="N84">
-        <v>-112.2081864</v>
+        <v>-113.8573716000001</v>
       </c>
       <c r="O84">
-        <v>-25.80788287200001</v>
+        <v>-26.18719546800001</v>
       </c>
       <c r="P84">
-        <v>-86.40030352800004</v>
+        <v>-87.67017613200004</v>
       </c>
       <c r="Q84">
-        <v>-21.30030352800004</v>
+        <v>-22.57017613200004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.468908526910797</v>
+        <v>0.4937972637879028</v>
       </c>
       <c r="T84">
-        <v>6.545354346673609</v>
+        <v>6.930375190595587</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03916013621342875</v>
+        <v>0.03868832734338743</v>
       </c>
       <c r="W84">
-        <v>0.2265660398808735</v>
+        <v>0.2266772924124293</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1702614617975162</v>
+        <v>0.1682101188842932</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8358,22 +8358,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2720876875462597</v>
+        <v>0.2739876875462598</v>
       </c>
       <c r="C85">
-        <v>-175.2053795332507</v>
+        <v>-183.8785434802785</v>
       </c>
       <c r="D85">
-        <v>238.7966204667494</v>
+        <v>237.1174565197216</v>
       </c>
       <c r="E85">
-        <v>544.3020000000001</v>
+        <v>551.296</v>
       </c>
       <c r="F85">
-        <v>580.5020000000002</v>
+        <v>587.4960000000001</v>
       </c>
       <c r="G85">
         <v>166.5</v>
@@ -8394,37 +8394,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M85">
-        <v>136.8823716000001</v>
+        <v>138.5315568</v>
       </c>
       <c r="N85">
-        <v>-113.8573716000001</v>
+        <v>-115.5065568</v>
       </c>
       <c r="O85">
-        <v>-26.18719546800001</v>
+        <v>-26.56650806400001</v>
       </c>
       <c r="P85">
-        <v>-87.67017613200004</v>
+        <v>-88.94004873600002</v>
       </c>
       <c r="Q85">
-        <v>-22.57017613200004</v>
+        <v>-23.84004873600003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4937972637879028</v>
+        <v>0.5217970927746468</v>
       </c>
       <c r="T85">
-        <v>6.930375190595587</v>
+        <v>7.363523640007813</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03868832734338743</v>
+        <v>0.03822775201787092</v>
       </c>
       <c r="W85">
-        <v>0.2266772924124293</v>
+        <v>0.2267858960741861</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1682101188842932</v>
+        <v>0.166207617469004</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8440,22 +8440,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2739876875462597</v>
+        <v>0.2758876875462597</v>
       </c>
       <c r="C86">
-        <v>-183.8785434802785</v>
+        <v>-192.5282573192808</v>
       </c>
       <c r="D86">
-        <v>237.1174565197216</v>
+        <v>235.4617426807192</v>
       </c>
       <c r="E86">
-        <v>551.296</v>
+        <v>558.29</v>
       </c>
       <c r="F86">
-        <v>587.4960000000001</v>
+        <v>594.49</v>
       </c>
       <c r="G86">
         <v>166.5</v>
@@ -8476,37 +8476,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M86">
-        <v>138.5315568</v>
+        <v>140.180742</v>
       </c>
       <c r="N86">
-        <v>-115.5065568</v>
+        <v>-117.155742</v>
       </c>
       <c r="O86">
-        <v>-26.56650806400001</v>
+        <v>-26.94582066</v>
       </c>
       <c r="P86">
-        <v>-88.94004873600002</v>
+        <v>-90.20992133999999</v>
       </c>
       <c r="Q86">
-        <v>-23.84004873600003</v>
+        <v>-25.10992134</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5217970927746465</v>
+        <v>0.5535302322929563</v>
       </c>
       <c r="T86">
-        <v>7.363523640007807</v>
+        <v>7.854425216008329</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03822775201787092</v>
+        <v>0.03777801375883715</v>
       </c>
       <c r="W86">
-        <v>0.2267858960741861</v>
+        <v>0.2268919443556662</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.166207617469004</v>
+        <v>0.1642522337340746</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8522,22 +8522,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2758876875462597</v>
+        <v>0.2777876875462597</v>
       </c>
       <c r="C87">
-        <v>-192.5282573192808</v>
+        <v>-201.155008877282</v>
       </c>
       <c r="D87">
-        <v>235.4617426807192</v>
+        <v>233.828991122718</v>
       </c>
       <c r="E87">
-        <v>558.29</v>
+        <v>565.284</v>
       </c>
       <c r="F87">
-        <v>594.49</v>
+        <v>601.484</v>
       </c>
       <c r="G87">
         <v>166.5</v>
@@ -8558,37 +8558,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M87">
-        <v>140.180742</v>
+        <v>141.8299272</v>
       </c>
       <c r="N87">
-        <v>-117.155742</v>
+        <v>-118.8049272</v>
       </c>
       <c r="O87">
-        <v>-26.94582066</v>
+        <v>-27.325133256</v>
       </c>
       <c r="P87">
-        <v>-90.20992133999999</v>
+        <v>-91.47979394400001</v>
       </c>
       <c r="Q87">
-        <v>-25.10992134</v>
+        <v>-26.37979394400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5535302322929563</v>
+        <v>0.5897966774567388</v>
       </c>
       <c r="T87">
-        <v>7.854425216008329</v>
+        <v>8.415455588580352</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03777801375883715</v>
+        <v>0.03733873452908323</v>
       </c>
       <c r="W87">
-        <v>0.2268919443556662</v>
+        <v>0.2269955263980422</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1642522337340746</v>
+        <v>0.1623423240394923</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8604,22 +8604,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2777876875462597</v>
+        <v>0.2796876875462597</v>
       </c>
       <c r="C88">
-        <v>-201.155008877282</v>
+        <v>-209.7592725436203</v>
       </c>
       <c r="D88">
-        <v>233.828991122718</v>
+        <v>232.2187274563798</v>
       </c>
       <c r="E88">
-        <v>565.284</v>
+        <v>572.278</v>
       </c>
       <c r="F88">
-        <v>601.484</v>
+        <v>608.4780000000001</v>
       </c>
       <c r="G88">
         <v>166.5</v>
@@ -8640,37 +8640,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M88">
-        <v>141.8299272</v>
+        <v>143.4791124</v>
       </c>
       <c r="N88">
-        <v>-118.8049272</v>
+        <v>-120.4541124</v>
       </c>
       <c r="O88">
-        <v>-27.325133256</v>
+        <v>-27.704445852</v>
       </c>
       <c r="P88">
-        <v>-91.47979394400001</v>
+        <v>-92.74966654800001</v>
       </c>
       <c r="Q88">
-        <v>-26.37979394400001</v>
+        <v>-27.64966654800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5897966774567388</v>
+        <v>0.6316425757226418</v>
       </c>
       <c r="T88">
-        <v>8.415455588580352</v>
+        <v>9.062798326163456</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03733873452908323</v>
+        <v>0.0369095536724271</v>
       </c>
       <c r="W88">
-        <v>0.2269955263980422</v>
+        <v>0.2270967272440417</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1623423240394923</v>
+        <v>0.1604763203149004</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8686,22 +8686,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2796876875462597</v>
+        <v>0.2815876875462597</v>
       </c>
       <c r="C89">
-        <v>-209.7592725436203</v>
+        <v>-218.3415097294768</v>
       </c>
       <c r="D89">
-        <v>232.2187274563798</v>
+        <v>230.6304902705233</v>
       </c>
       <c r="E89">
-        <v>572.278</v>
+        <v>579.272</v>
       </c>
       <c r="F89">
-        <v>608.4780000000001</v>
+        <v>615.4720000000001</v>
       </c>
       <c r="G89">
         <v>166.5</v>
@@ -8722,37 +8722,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M89">
-        <v>143.4791124</v>
+        <v>145.1282976</v>
       </c>
       <c r="N89">
-        <v>-120.4541124</v>
+        <v>-122.1032976</v>
       </c>
       <c r="O89">
-        <v>-27.704445852</v>
+        <v>-28.083758448</v>
       </c>
       <c r="P89">
-        <v>-92.74966654800001</v>
+        <v>-94.01953915200002</v>
       </c>
       <c r="Q89">
-        <v>-27.64966654800001</v>
+        <v>-28.91953915200003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6316425757226418</v>
+        <v>0.6804627903661954</v>
       </c>
       <c r="T89">
-        <v>9.062798326163456</v>
+        <v>9.818031520010413</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0369095536724271</v>
+        <v>0.03649012692614952</v>
       </c>
       <c r="W89">
-        <v>0.2270967272440417</v>
+        <v>0.2271956280708139</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1604763203149004</v>
+        <v>0.1586527257658674</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8768,22 +8768,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2815876875462597</v>
+        <v>0.2834876875462597</v>
       </c>
       <c r="C90">
-        <v>-218.3415097294768</v>
+        <v>-226.9021693086748</v>
       </c>
       <c r="D90">
-        <v>230.6304902705233</v>
+        <v>229.0638306913253</v>
       </c>
       <c r="E90">
-        <v>579.272</v>
+        <v>586.2660000000001</v>
       </c>
       <c r="F90">
-        <v>615.4720000000001</v>
+        <v>622.4660000000001</v>
       </c>
       <c r="G90">
         <v>166.5</v>
@@ -8804,37 +8804,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M90">
-        <v>145.1282976</v>
+        <v>146.7774828</v>
       </c>
       <c r="N90">
-        <v>-122.1032976</v>
+        <v>-123.7524828</v>
       </c>
       <c r="O90">
-        <v>-28.083758448</v>
+        <v>-28.46307104400001</v>
       </c>
       <c r="P90">
-        <v>-94.01953915200002</v>
+        <v>-95.28941175600002</v>
       </c>
       <c r="Q90">
-        <v>-28.91953915200003</v>
+        <v>-30.18941175600003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6804627903661954</v>
+        <v>0.7381594076722132</v>
       </c>
       <c r="T90">
-        <v>9.818031520010413</v>
+        <v>10.71057984001136</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03649012692614952</v>
+        <v>0.03608012550001301</v>
       </c>
       <c r="W90">
-        <v>0.2271956280708139</v>
+        <v>0.2272923064070969</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1586527257658674</v>
+        <v>0.1568701108696218</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8850,22 +8850,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2834876875462597</v>
+        <v>0.2853876875462597</v>
       </c>
       <c r="C91">
-        <v>-226.9021693086748</v>
+        <v>-235.4416880406343</v>
       </c>
       <c r="D91">
-        <v>229.0638306913253</v>
+        <v>227.5183119593659</v>
       </c>
       <c r="E91">
-        <v>586.2660000000001</v>
+        <v>593.2600000000001</v>
       </c>
       <c r="F91">
-        <v>622.4660000000001</v>
+        <v>629.4600000000002</v>
       </c>
       <c r="G91">
         <v>166.5</v>
@@ -8886,37 +8886,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M91">
-        <v>146.7774828</v>
+        <v>148.426668</v>
       </c>
       <c r="N91">
-        <v>-123.7524828</v>
+        <v>-125.401668</v>
       </c>
       <c r="O91">
-        <v>-28.46307104400001</v>
+        <v>-28.84238364000001</v>
       </c>
       <c r="P91">
-        <v>-95.28941175600002</v>
+        <v>-96.55928436000002</v>
       </c>
       <c r="Q91">
-        <v>-30.18941175600003</v>
+        <v>-31.45928436000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7381594076722132</v>
+        <v>0.8073953484394345</v>
       </c>
       <c r="T91">
-        <v>10.71057984001136</v>
+        <v>11.7816378240125</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03608012550001301</v>
+        <v>0.03567923521667953</v>
       </c>
       <c r="W91">
-        <v>0.2272923064070969</v>
+        <v>0.227386836335907</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1568701108696218</v>
+        <v>0.155127109637737</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8932,22 +8932,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2853876875462597</v>
+        <v>0.2872876875462597</v>
       </c>
       <c r="C92">
-        <v>-235.4416880406343</v>
+        <v>-243.9604909763191</v>
       </c>
       <c r="D92">
-        <v>227.5183119593659</v>
+        <v>225.9935090236809</v>
       </c>
       <c r="E92">
-        <v>593.2600000000001</v>
+        <v>600.254</v>
       </c>
       <c r="F92">
-        <v>629.4600000000002</v>
+        <v>636.4540000000001</v>
       </c>
       <c r="G92">
         <v>166.5</v>
@@ -8968,37 +8968,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M92">
-        <v>148.426668</v>
+        <v>150.0758532</v>
       </c>
       <c r="N92">
-        <v>-125.401668</v>
+        <v>-127.0508532</v>
       </c>
       <c r="O92">
-        <v>-28.84238364000001</v>
+        <v>-29.221696236</v>
       </c>
       <c r="P92">
-        <v>-96.55928436000002</v>
+        <v>-97.82915696400001</v>
       </c>
       <c r="Q92">
-        <v>-31.45928436000003</v>
+        <v>-32.72915696400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8073953484394345</v>
+        <v>0.892017053821594</v>
       </c>
       <c r="T92">
-        <v>11.7816378240125</v>
+        <v>13.09070869334722</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03567923521667953</v>
+        <v>0.03528715570880393</v>
       </c>
       <c r="W92">
-        <v>0.227386836335907</v>
+        <v>0.2274792886838641</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.155127109637737</v>
+        <v>0.1534224161252344</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9014,22 +9014,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2872876875462597</v>
+        <v>0.2891876875462597</v>
       </c>
       <c r="C93">
-        <v>-243.9604909763191</v>
+        <v>-252.4589918479692</v>
       </c>
       <c r="D93">
-        <v>225.9935090236809</v>
+        <v>224.4890081520309</v>
       </c>
       <c r="E93">
-        <v>600.254</v>
+        <v>607.248</v>
       </c>
       <c r="F93">
-        <v>636.4540000000001</v>
+        <v>643.4480000000001</v>
       </c>
       <c r="G93">
         <v>166.5</v>
@@ -9050,37 +9050,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M93">
-        <v>150.0758532</v>
+        <v>151.7250384</v>
       </c>
       <c r="N93">
-        <v>-127.0508532</v>
+        <v>-128.7000384</v>
       </c>
       <c r="O93">
-        <v>-29.221696236</v>
+        <v>-29.60100883200001</v>
       </c>
       <c r="P93">
-        <v>-97.82915696400001</v>
+        <v>-99.09902956800001</v>
       </c>
       <c r="Q93">
-        <v>-32.72915696400001</v>
+        <v>-33.99902956800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.892017053821594</v>
+        <v>0.9977941855492936</v>
       </c>
       <c r="T93">
-        <v>13.09070869334722</v>
+        <v>14.72704728001563</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03528715570880393</v>
+        <v>0.03490359966849085</v>
       </c>
       <c r="W93">
-        <v>0.2274792886838641</v>
+        <v>0.2275697311981699</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1534224161252344</v>
+        <v>0.1517547811673515</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9096,22 +9096,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2891876875462597</v>
+        <v>0.2910876875462597</v>
       </c>
       <c r="C94">
-        <v>-252.4589918479692</v>
+        <v>-260.9375934433676</v>
       </c>
       <c r="D94">
-        <v>224.4890081520309</v>
+        <v>223.0044065566325</v>
       </c>
       <c r="E94">
-        <v>607.248</v>
+        <v>614.2420000000001</v>
       </c>
       <c r="F94">
-        <v>643.4480000000001</v>
+        <v>650.4420000000001</v>
       </c>
       <c r="G94">
         <v>166.5</v>
@@ -9132,37 +9132,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M94">
-        <v>151.7250384</v>
+        <v>153.3742236</v>
       </c>
       <c r="N94">
-        <v>-128.7000384</v>
+        <v>-130.3492236</v>
       </c>
       <c r="O94">
-        <v>-29.60100883200001</v>
+        <v>-29.980321428</v>
       </c>
       <c r="P94">
-        <v>-99.09902956800001</v>
+        <v>-100.368902172</v>
       </c>
       <c r="Q94">
-        <v>-33.99902956800001</v>
+        <v>-35.26890217200003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9977941855492936</v>
+        <v>1.133793354913479</v>
       </c>
       <c r="T94">
-        <v>14.72704728001563</v>
+        <v>16.83091117716072</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03490359966849085</v>
+        <v>0.03452829214517374</v>
       </c>
       <c r="W94">
-        <v>0.2275697311981699</v>
+        <v>0.227658228712168</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1517547811673515</v>
+        <v>0.1501230093268423</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9178,22 +9178,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2910876875462597</v>
+        <v>0.2929876875462598</v>
       </c>
       <c r="C95">
-        <v>-260.9375934433676</v>
+        <v>-269.3966879653558</v>
       </c>
       <c r="D95">
-        <v>223.0044065566325</v>
+        <v>221.5393120346444</v>
       </c>
       <c r="E95">
-        <v>614.2420000000001</v>
+        <v>621.2360000000001</v>
       </c>
       <c r="F95">
-        <v>650.4420000000001</v>
+        <v>657.4360000000001</v>
       </c>
       <c r="G95">
         <v>166.5</v>
@@ -9214,37 +9214,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M95">
-        <v>153.3742236</v>
+        <v>155.0234088000001</v>
       </c>
       <c r="N95">
-        <v>-130.3492236</v>
+        <v>-131.9984088</v>
       </c>
       <c r="O95">
-        <v>-29.980321428</v>
+        <v>-30.35963402400001</v>
       </c>
       <c r="P95">
-        <v>-100.368902172</v>
+        <v>-101.638774776</v>
       </c>
       <c r="Q95">
-        <v>-35.26890217200003</v>
+        <v>-36.53877477600004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.133793354913479</v>
+        <v>1.315125580732392</v>
       </c>
       <c r="T95">
-        <v>16.83091117716072</v>
+        <v>19.63606304002084</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03452829214517374</v>
+        <v>0.03416096988831018</v>
       </c>
       <c r="W95">
-        <v>0.227658228712168</v>
+        <v>0.2277448433003365</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1501230093268423</v>
+        <v>0.1485259560361312</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9260,22 +9260,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2929876875462598</v>
+        <v>0.2948876875462598</v>
       </c>
       <c r="C96">
-        <v>-269.3966879653558</v>
+        <v>-277.8366573772685</v>
       </c>
       <c r="D96">
-        <v>221.5393120346444</v>
+        <v>220.0933426227317</v>
       </c>
       <c r="E96">
-        <v>621.2360000000001</v>
+        <v>628.2300000000001</v>
       </c>
       <c r="F96">
-        <v>657.4360000000001</v>
+        <v>664.4300000000002</v>
       </c>
       <c r="G96">
         <v>166.5</v>
@@ -9296,37 +9296,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M96">
-        <v>155.0234088000001</v>
+        <v>156.6725940000001</v>
       </c>
       <c r="N96">
-        <v>-131.9984088</v>
+        <v>-133.6475940000001</v>
       </c>
       <c r="O96">
-        <v>-30.35963402400001</v>
+        <v>-30.73894662000001</v>
       </c>
       <c r="P96">
-        <v>-101.638774776</v>
+        <v>-102.90864738</v>
       </c>
       <c r="Q96">
-        <v>-36.53877477600004</v>
+        <v>-37.80864738000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.315125580732392</v>
+        <v>1.568990696878871</v>
       </c>
       <c r="T96">
-        <v>19.63606304002084</v>
+        <v>23.56327564802502</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03416096988831018</v>
+        <v>0.03380138073159113</v>
       </c>
       <c r="W96">
-        <v>0.2277448433003365</v>
+        <v>0.2278296344234908</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1485259560361312</v>
+        <v>0.1469625249199614</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9342,22 +9342,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2948876875462598</v>
+        <v>0.2967876875462597</v>
       </c>
       <c r="C97">
-        <v>-277.8366573772685</v>
+        <v>-286.257873734929</v>
       </c>
       <c r="D97">
-        <v>220.0933426227317</v>
+        <v>218.6661262650711</v>
       </c>
       <c r="E97">
-        <v>628.2300000000001</v>
+        <v>635.224</v>
       </c>
       <c r="F97">
-        <v>664.4300000000002</v>
+        <v>671.4240000000001</v>
       </c>
       <c r="G97">
         <v>166.5</v>
@@ -9378,37 +9378,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M97">
-        <v>156.6725940000001</v>
+        <v>158.3217792</v>
       </c>
       <c r="N97">
-        <v>-133.6475940000001</v>
+        <v>-135.2967792</v>
       </c>
       <c r="O97">
-        <v>-30.73894662000001</v>
+        <v>-31.11825921600001</v>
       </c>
       <c r="P97">
-        <v>-102.90864738</v>
+        <v>-104.178519984</v>
       </c>
       <c r="Q97">
-        <v>-37.80864738000005</v>
+        <v>-39.07851998400002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.568990696878871</v>
+        <v>1.94978837109859</v>
       </c>
       <c r="T97">
-        <v>23.56327564802502</v>
+        <v>29.45409456003129</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03380138073159113</v>
+        <v>0.03344928301563706</v>
       </c>
       <c r="W97">
-        <v>0.2278296344234908</v>
+        <v>0.2279126590649128</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1469625249199614</v>
+        <v>0.1454316652853785</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9424,22 +9424,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2967876875462597</v>
+        <v>0.2986876875462597</v>
       </c>
       <c r="C98">
-        <v>-286.257873734929</v>
+        <v>-294.6606995058112</v>
       </c>
       <c r="D98">
-        <v>218.6661262650711</v>
+        <v>217.2573004941889</v>
       </c>
       <c r="E98">
-        <v>635.224</v>
+        <v>642.2180000000001</v>
       </c>
       <c r="F98">
-        <v>671.4240000000001</v>
+        <v>678.4180000000001</v>
       </c>
       <c r="G98">
         <v>166.5</v>
@@ -9460,37 +9460,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M98">
-        <v>158.3217792</v>
+        <v>159.9709644</v>
       </c>
       <c r="N98">
-        <v>-135.2967792</v>
+        <v>-136.9459644</v>
       </c>
       <c r="O98">
-        <v>-31.11825921600001</v>
+        <v>-31.49757181200001</v>
       </c>
       <c r="P98">
-        <v>-104.178519984</v>
+        <v>-105.448392588</v>
       </c>
       <c r="Q98">
-        <v>-39.07851998400002</v>
+        <v>-40.34839258800002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.949788371098585</v>
+        <v>2.584451161464779</v>
       </c>
       <c r="T98">
-        <v>29.45409456003121</v>
+        <v>39.27212608004162</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03344928301563706</v>
+        <v>0.03310444504640369</v>
       </c>
       <c r="W98">
-        <v>0.2279126590649128</v>
+        <v>0.227993971858058</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1454316652853785</v>
+        <v>0.1439323697669725</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9506,22 +9506,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2986876875462597</v>
+        <v>0.3005876875462598</v>
       </c>
       <c r="C99">
-        <v>-294.6606995058112</v>
+        <v>-303.045487875941</v>
       </c>
       <c r="D99">
-        <v>217.2573004941889</v>
+        <v>215.866512124059</v>
       </c>
       <c r="E99">
-        <v>642.2180000000001</v>
+        <v>649.212</v>
       </c>
       <c r="F99">
-        <v>678.4180000000001</v>
+        <v>685.412</v>
       </c>
       <c r="G99">
         <v>166.5</v>
@@ -9542,37 +9542,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M99">
-        <v>159.9709644</v>
+        <v>161.6201496</v>
       </c>
       <c r="N99">
-        <v>-136.9459644</v>
+        <v>-138.5951496</v>
       </c>
       <c r="O99">
-        <v>-31.49757181200001</v>
+        <v>-31.87688440800001</v>
       </c>
       <c r="P99">
-        <v>-105.448392588</v>
+        <v>-106.718265192</v>
       </c>
       <c r="Q99">
-        <v>-40.34839258800002</v>
+        <v>-41.61826519200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.584451161464779</v>
+        <v>3.853776742197169</v>
       </c>
       <c r="T99">
-        <v>39.27212608004162</v>
+        <v>58.90818912006242</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03310444504640369</v>
+        <v>0.03276664458674651</v>
       </c>
       <c r="W99">
-        <v>0.227993971858058</v>
+        <v>0.2280736252064452</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1439323697669725</v>
+        <v>0.1424636721162892</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9588,22 +9588,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3005876875462598</v>
+        <v>0.3024876875462597</v>
       </c>
       <c r="C100">
-        <v>-303.045487875941</v>
+        <v>-311.4125830450873</v>
       </c>
       <c r="D100">
-        <v>215.866512124059</v>
+        <v>214.4934169549128</v>
       </c>
       <c r="E100">
-        <v>649.212</v>
+        <v>656.206</v>
       </c>
       <c r="F100">
-        <v>685.412</v>
+        <v>692.4060000000001</v>
       </c>
       <c r="G100">
         <v>166.5</v>
@@ -9624,37 +9624,37 @@
         <v>23.02500000000001</v>
       </c>
       <c r="M100">
-        <v>161.6201496</v>
+        <v>163.2693348</v>
       </c>
       <c r="N100">
-        <v>-138.5951496</v>
+        <v>-140.2443348</v>
       </c>
       <c r="O100">
-        <v>-31.87688440800001</v>
+        <v>-32.25619700400001</v>
       </c>
       <c r="P100">
-        <v>-106.718265192</v>
+        <v>-107.988137796</v>
       </c>
       <c r="Q100">
-        <v>-41.61826519200001</v>
+        <v>-42.88813779600002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.853776742197169</v>
+        <v>7.661753484394338</v>
       </c>
       <c r="T100">
-        <v>58.90818912006242</v>
+        <v>117.8163782401248</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03276664458674651</v>
+        <v>0.03243566837879958</v>
       </c>
       <c r="W100">
-        <v>0.2280736252064452</v>
+        <v>0.2281516693962791</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9662,91 +9662,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1424636721162892</v>
+        <v>0.1410246451252155</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3024876875462597</v>
-      </c>
-      <c r="C101">
-        <v>-311.4125830450873</v>
-      </c>
-      <c r="D101">
-        <v>214.4934169549128</v>
-      </c>
-      <c r="E101">
-        <v>656.206</v>
-      </c>
-      <c r="F101">
-        <v>692.4060000000001</v>
-      </c>
-      <c r="G101">
-        <v>166.5</v>
-      </c>
-      <c r="H101">
-        <v>663.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>88.125</v>
-      </c>
-      <c r="K101">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>23.02500000000001</v>
-      </c>
-      <c r="M101">
-        <v>163.2693348</v>
-      </c>
-      <c r="N101">
-        <v>-140.2443348</v>
-      </c>
-      <c r="O101">
-        <v>-32.25619700400001</v>
-      </c>
-      <c r="P101">
-        <v>-107.988137796</v>
-      </c>
-      <c r="Q101">
-        <v>-42.88813779600002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.661753484394338</v>
-      </c>
-      <c r="T101">
-        <v>117.8163782401248</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03243566837879958</v>
-      </c>
-      <c r="W101">
-        <v>0.2281516693962791</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1410246451252155</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
